--- a/data/finance-report-042024.xlsx
+++ b/data/finance-report-042024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marya/Documents/ESILV/A4/S8/Pi2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marya/Documents/ESILV/A4/S8/Pi2/pi2-zacca/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDFBBC4-CD1B-1F4B-B114-F295A327E0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4F1443-F0C5-B642-9C7D-4E33BCDAE322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11180" yWindow="-28800" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Budget in TRY" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="356">
   <si>
     <t>!!Please insert lines under the sub-headings if necessary!!</t>
   </si>
@@ -1118,18 +1118,6 @@
   </si>
   <si>
     <t>Indirect Cost April24</t>
-  </si>
-  <si>
-    <t>Velocity Score</t>
-  </si>
-  <si>
-    <t>Transactions per day</t>
-  </si>
-  <si>
-    <t>Average Total Amount In USD</t>
-  </si>
-  <si>
-    <t>Relative deviation</t>
   </si>
 </sst>
 </file>
@@ -2188,7 +2176,7 @@
     <xf numFmtId="165" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="377">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3155,70 +3143,54 @@
     <xf numFmtId="176" fontId="40" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="39" fillId="7" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="31" fillId="8" borderId="41" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="36" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="19" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3245,30 +3217,34 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="19" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -3718,41 +3694,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="38.25" customHeight="1">
-      <c r="A1" s="350" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="351"/>
-      <c r="C1" s="355" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="337"/>
-      <c r="E1" s="337"/>
-      <c r="F1" s="338"/>
+      <c r="A1" s="370" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="371"/>
+      <c r="C1" s="350" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="340"/>
       <c r="G1" s="130"/>
-      <c r="H1" s="359" t="s">
+      <c r="H1" s="353" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="337"/>
-      <c r="J1" s="338"/>
-      <c r="K1" s="343"/>
-      <c r="L1" s="337"/>
-      <c r="M1" s="338"/>
-      <c r="N1" s="352" t="s">
+      <c r="I1" s="339"/>
+      <c r="J1" s="340"/>
+      <c r="K1" s="366"/>
+      <c r="L1" s="339"/>
+      <c r="M1" s="340"/>
+      <c r="N1" s="372" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="337"/>
-      <c r="P1" s="337"/>
-      <c r="Q1" s="337"/>
-      <c r="R1" s="337"/>
-      <c r="S1" s="338"/>
+      <c r="O1" s="339"/>
+      <c r="P1" s="339"/>
+      <c r="Q1" s="339"/>
+      <c r="R1" s="339"/>
+      <c r="S1" s="340"/>
       <c r="T1" s="131"/>
-      <c r="U1" s="336" t="s">
+      <c r="U1" s="362" t="s">
         <v>4</v>
       </c>
-      <c r="V1" s="337"/>
-      <c r="W1" s="337"/>
-      <c r="X1" s="337"/>
-      <c r="Y1" s="338"/>
+      <c r="V1" s="339"/>
+      <c r="W1" s="339"/>
+      <c r="X1" s="339"/>
+      <c r="Y1" s="340"/>
       <c r="Z1" s="12"/>
       <c r="AA1" s="12"/>
       <c r="AB1" s="12"/>
@@ -3770,10 +3746,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="9"/>
-      <c r="C2" s="341"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="338"/>
+      <c r="C2" s="364"/>
+      <c r="D2" s="339"/>
+      <c r="E2" s="339"/>
+      <c r="F2" s="340"/>
       <c r="G2" s="130"/>
       <c r="H2" s="132"/>
       <c r="I2" s="132"/>
@@ -3785,13 +3761,13 @@
       <c r="O2" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="357">
+      <c r="P2" s="344">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="337"/>
-      <c r="R2" s="337"/>
-      <c r="S2" s="338"/>
+      <c r="Q2" s="339"/>
+      <c r="R2" s="339"/>
+      <c r="S2" s="340"/>
       <c r="T2" s="133"/>
       <c r="U2" s="134"/>
       <c r="V2" s="134"/>
@@ -3815,32 +3791,32 @@
         <v>6</v>
       </c>
       <c r="B3" s="127"/>
-      <c r="C3" s="371"/>
-      <c r="D3" s="337"/>
-      <c r="E3" s="337"/>
-      <c r="F3" s="338"/>
+      <c r="C3" s="338"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="340"/>
       <c r="G3" s="130"/>
-      <c r="H3" s="358" t="s">
+      <c r="H3" s="352" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="354"/>
+      <c r="I3" s="335"/>
       <c r="J3" s="135"/>
-      <c r="K3" s="342" t="s">
+      <c r="K3" s="365" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="338"/>
+      <c r="L3" s="340"/>
       <c r="M3" s="13"/>
       <c r="N3" s="87"/>
       <c r="O3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="376">
+      <c r="P3" s="348">
         <f>C3</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="338"/>
+      <c r="Q3" s="339"/>
+      <c r="R3" s="339"/>
+      <c r="S3" s="340"/>
       <c r="T3" s="133"/>
       <c r="U3" s="136"/>
       <c r="V3" s="136"/>
@@ -3864,38 +3840,38 @@
         <v>9</v>
       </c>
       <c r="B4" s="10"/>
-      <c r="C4" s="362"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="364"/>
+      <c r="C4" s="356"/>
+      <c r="D4" s="357"/>
+      <c r="E4" s="357"/>
+      <c r="F4" s="358"/>
       <c r="G4" s="130"/>
       <c r="H4" s="132"/>
       <c r="I4" s="132"/>
       <c r="J4" s="132"/>
-      <c r="K4" s="340" t="s">
+      <c r="K4" s="363" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="338"/>
+      <c r="L4" s="340"/>
       <c r="M4" s="13"/>
       <c r="N4" s="88"/>
       <c r="O4" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="357">
+      <c r="P4" s="344">
         <f>C4</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="338"/>
+      <c r="Q4" s="339"/>
+      <c r="R4" s="339"/>
+      <c r="S4" s="340"/>
       <c r="T4" s="133"/>
       <c r="U4" s="134"/>
       <c r="V4" s="134"/>
       <c r="W4" s="134"/>
-      <c r="X4" s="344" t="s">
+      <c r="X4" s="367" t="s">
         <v>10</v>
       </c>
-      <c r="Y4" s="338"/>
+      <c r="Y4" s="340"/>
       <c r="Z4" s="12"/>
       <c r="AA4" s="12"/>
       <c r="AB4" s="12"/>
@@ -4669,10 +4645,10 @@
       <c r="AJ15" s="12"/>
     </row>
     <row r="16" spans="1:36" ht="21" customHeight="1" thickBot="1">
-      <c r="A16" s="345" t="s">
+      <c r="A16" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="346"/>
+      <c r="B16" s="336"/>
       <c r="C16" s="39"/>
       <c r="D16" s="39"/>
       <c r="E16" s="195"/>
@@ -4702,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="M16" s="40"/>
-      <c r="N16" s="374" t="s">
+      <c r="N16" s="346" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="346"/>
+      <c r="O16" s="336"/>
       <c r="P16" s="41"/>
       <c r="Q16" s="41"/>
       <c r="R16" s="202"/>
@@ -4959,10 +4935,10 @@
       <c r="AJ19" s="12"/>
     </row>
     <row r="20" spans="1:36" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A20" s="345" t="s">
+      <c r="A20" s="337" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="346"/>
+      <c r="B20" s="336"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
       <c r="E20" s="195"/>
@@ -4992,10 +4968,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="40"/>
-      <c r="N20" s="374" t="s">
+      <c r="N20" s="346" t="s">
         <v>51</v>
       </c>
-      <c r="O20" s="346"/>
+      <c r="O20" s="336"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="41"/>
       <c r="R20" s="202"/>
@@ -5399,10 +5375,10 @@
       <c r="AJ25" s="12"/>
     </row>
     <row r="26" spans="1:36" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A26" s="361" t="s">
+      <c r="A26" s="355" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="354"/>
+      <c r="B26" s="335"/>
       <c r="C26" s="39"/>
       <c r="D26" s="39"/>
       <c r="E26" s="195"/>
@@ -5432,10 +5408,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="40"/>
-      <c r="N26" s="373" t="s">
+      <c r="N26" s="345" t="s">
         <v>59</v>
       </c>
-      <c r="O26" s="354"/>
+      <c r="O26" s="335"/>
       <c r="P26" s="41"/>
       <c r="Q26" s="41"/>
       <c r="R26" s="202"/>
@@ -5911,10 +5887,10 @@
       <c r="AJ32" s="12"/>
     </row>
     <row r="33" spans="1:36" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A33" s="365" t="s">
+      <c r="A33" s="359" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="366"/>
+      <c r="B33" s="360"/>
       <c r="C33" s="90"/>
       <c r="D33" s="39"/>
       <c r="E33" s="195"/>
@@ -5944,10 +5920,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="40"/>
-      <c r="N33" s="373" t="s">
+      <c r="N33" s="345" t="s">
         <v>70</v>
       </c>
-      <c r="O33" s="354"/>
+      <c r="O33" s="335"/>
       <c r="P33" s="41"/>
       <c r="Q33" s="41"/>
       <c r="R33" s="202"/>
@@ -5989,11 +5965,11 @@
       <c r="AJ33" s="12"/>
     </row>
     <row r="34" spans="1:36" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A34" s="356" t="s">
+      <c r="A34" s="351" t="s">
         <v>71</v>
       </c>
-      <c r="B34" s="337"/>
-      <c r="C34" s="338"/>
+      <c r="B34" s="339"/>
+      <c r="C34" s="340"/>
       <c r="D34" s="39"/>
       <c r="E34" s="195"/>
       <c r="F34" s="196"/>
@@ -6004,11 +5980,11 @@
       <c r="K34" s="201"/>
       <c r="L34" s="196"/>
       <c r="M34" s="40"/>
-      <c r="N34" s="374" t="s">
+      <c r="N34" s="346" t="s">
         <v>71</v>
       </c>
-      <c r="O34" s="354"/>
-      <c r="P34" s="346"/>
+      <c r="O34" s="335"/>
+      <c r="P34" s="336"/>
       <c r="Q34" s="41"/>
       <c r="R34" s="202"/>
       <c r="S34" s="203"/>
@@ -6046,10 +6022,10 @@
       <c r="AJ34" s="12"/>
     </row>
     <row r="35" spans="1:36" s="83" customFormat="1" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A35" s="347" t="s">
+      <c r="A35" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="348"/>
+      <c r="B35" s="369"/>
       <c r="C35" s="91"/>
       <c r="D35" s="58"/>
       <c r="E35" s="226"/>
@@ -6079,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="59"/>
-      <c r="N35" s="375" t="s">
+      <c r="N35" s="347" t="s">
         <v>72</v>
       </c>
-      <c r="O35" s="354"/>
+      <c r="O35" s="335"/>
       <c r="P35" s="60"/>
       <c r="Q35" s="61"/>
       <c r="R35" s="233"/>
@@ -6162,10 +6138,10 @@
       <c r="AJ36" s="12"/>
     </row>
     <row r="37" spans="1:36" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A37" s="372" t="s">
+      <c r="A37" s="343" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="369"/>
+      <c r="B37" s="333"/>
       <c r="C37" s="70" t="s">
         <v>74</v>
       </c>
@@ -6195,10 +6171,10 @@
         <v>82</v>
       </c>
       <c r="M37" s="71"/>
-      <c r="N37" s="368" t="s">
+      <c r="N37" s="332" t="s">
         <v>73</v>
       </c>
-      <c r="O37" s="369"/>
+      <c r="O37" s="333"/>
       <c r="P37" s="72" t="s">
         <v>74</v>
       </c>
@@ -6238,12 +6214,12 @@
       <c r="AJ37" s="12"/>
     </row>
     <row r="38" spans="1:36" ht="16.5" customHeight="1">
-      <c r="A38" s="339" t="s">
+      <c r="A38" s="342" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="337"/>
-      <c r="C38" s="337"/>
-      <c r="D38" s="338"/>
+      <c r="B38" s="339"/>
+      <c r="C38" s="339"/>
+      <c r="D38" s="340"/>
       <c r="E38" s="267" t="e">
         <f t="shared" ref="E38:E44" si="6">F38/$F$45</f>
         <v>#DIV/0!</v>
@@ -6262,12 +6238,12 @@
         <v>0</v>
       </c>
       <c r="M38" s="40"/>
-      <c r="N38" s="349" t="s">
+      <c r="N38" s="341" t="s">
         <v>85</v>
       </c>
-      <c r="O38" s="337"/>
-      <c r="P38" s="337"/>
-      <c r="Q38" s="338"/>
+      <c r="O38" s="339"/>
+      <c r="P38" s="339"/>
+      <c r="Q38" s="340"/>
       <c r="R38" s="73" t="e">
         <f t="shared" ref="R38:R44" si="9">S38/$S$45</f>
         <v>#DIV/0!</v>
@@ -6310,10 +6286,10 @@
       <c r="AJ38" s="12"/>
     </row>
     <row r="39" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A39" s="339" t="s">
+      <c r="A39" s="342" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="338"/>
+      <c r="B39" s="340"/>
       <c r="C39" s="276"/>
       <c r="D39" s="276"/>
       <c r="E39" s="267" t="e">
@@ -6334,10 +6310,10 @@
         <v>0</v>
       </c>
       <c r="M39" s="40"/>
-      <c r="N39" s="349" t="s">
+      <c r="N39" s="341" t="s">
         <v>86</v>
       </c>
-      <c r="O39" s="338"/>
+      <c r="O39" s="340"/>
       <c r="P39" s="277"/>
       <c r="Q39" s="277"/>
       <c r="R39" s="73" t="e">
@@ -6382,10 +6358,10 @@
       <c r="AJ39" s="12"/>
     </row>
     <row r="40" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A40" s="339" t="s">
+      <c r="A40" s="342" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="338"/>
+      <c r="B40" s="340"/>
       <c r="C40" s="276"/>
       <c r="D40" s="276"/>
       <c r="E40" s="267" t="e">
@@ -6406,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="M40" s="40"/>
-      <c r="N40" s="349" t="s">
+      <c r="N40" s="341" t="s">
         <v>86</v>
       </c>
-      <c r="O40" s="338"/>
+      <c r="O40" s="340"/>
       <c r="P40" s="277"/>
       <c r="Q40" s="277"/>
       <c r="R40" s="73" t="e">
@@ -6454,10 +6430,10 @@
       <c r="AJ40" s="12"/>
     </row>
     <row r="41" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A41" s="339" t="s">
+      <c r="A41" s="342" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="338"/>
+      <c r="B41" s="340"/>
       <c r="C41" s="276"/>
       <c r="D41" s="276"/>
       <c r="E41" s="267" t="e">
@@ -6478,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="M41" s="40"/>
-      <c r="N41" s="349" t="s">
+      <c r="N41" s="341" t="s">
         <v>86</v>
       </c>
-      <c r="O41" s="338"/>
+      <c r="O41" s="340"/>
       <c r="P41" s="277"/>
       <c r="Q41" s="277"/>
       <c r="R41" s="73" t="e">
@@ -6526,10 +6502,10 @@
       <c r="AJ41" s="12"/>
     </row>
     <row r="42" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A42" s="339" t="s">
+      <c r="A42" s="342" t="s">
         <v>86</v>
       </c>
-      <c r="B42" s="338"/>
+      <c r="B42" s="340"/>
       <c r="C42" s="276"/>
       <c r="D42" s="276"/>
       <c r="E42" s="267" t="e">
@@ -6550,10 +6526,10 @@
         <v>0</v>
       </c>
       <c r="M42" s="40"/>
-      <c r="N42" s="349" t="s">
+      <c r="N42" s="341" t="s">
         <v>86</v>
       </c>
-      <c r="O42" s="338"/>
+      <c r="O42" s="340"/>
       <c r="P42" s="277"/>
       <c r="Q42" s="277"/>
       <c r="R42" s="73" t="e">
@@ -6598,10 +6574,10 @@
       <c r="AJ42" s="12"/>
     </row>
     <row r="43" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A43" s="339" t="s">
+      <c r="A43" s="342" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="338"/>
+      <c r="B43" s="340"/>
       <c r="C43" s="276"/>
       <c r="D43" s="276"/>
       <c r="E43" s="267" t="e">
@@ -6622,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="M43" s="40"/>
-      <c r="N43" s="349" t="s">
+      <c r="N43" s="341" t="s">
         <v>87</v>
       </c>
-      <c r="O43" s="338"/>
+      <c r="O43" s="340"/>
       <c r="P43" s="277"/>
       <c r="Q43" s="277"/>
       <c r="R43" s="73" t="e">
@@ -6670,10 +6646,10 @@
       <c r="AJ43" s="12"/>
     </row>
     <row r="44" spans="1:36" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A44" s="339" t="s">
+      <c r="A44" s="342" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="338"/>
+      <c r="B44" s="340"/>
       <c r="C44" s="276"/>
       <c r="D44" s="276"/>
       <c r="E44" s="278" t="e">
@@ -6694,10 +6670,10 @@
         <v>0</v>
       </c>
       <c r="M44" s="40"/>
-      <c r="N44" s="349" t="s">
+      <c r="N44" s="341" t="s">
         <v>87</v>
       </c>
-      <c r="O44" s="338"/>
+      <c r="O44" s="340"/>
       <c r="P44" s="277"/>
       <c r="Q44" s="277"/>
       <c r="R44" s="73" t="e">
@@ -6742,12 +6718,12 @@
       <c r="AJ44" s="12"/>
     </row>
     <row r="45" spans="1:36" s="83" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A45" s="360" t="s">
+      <c r="A45" s="354" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="354"/>
-      <c r="C45" s="354"/>
-      <c r="D45" s="346"/>
+      <c r="B45" s="335"/>
+      <c r="C45" s="335"/>
+      <c r="D45" s="336"/>
       <c r="E45" s="283" t="e">
         <f>SUM(E38:E44)</f>
         <v>#DIV/0!</v>
@@ -6778,12 +6754,12 @@
         <v>0</v>
       </c>
       <c r="M45" s="59"/>
-      <c r="N45" s="370" t="s">
+      <c r="N45" s="334" t="s">
         <v>88</v>
       </c>
-      <c r="O45" s="354"/>
-      <c r="P45" s="354"/>
-      <c r="Q45" s="346"/>
+      <c r="O45" s="335"/>
+      <c r="P45" s="335"/>
+      <c r="Q45" s="336"/>
       <c r="R45" s="74" t="e">
         <f>SUM(R38:R44)</f>
         <v>#DIV/0!</v>
@@ -6868,13 +6844,13 @@
       <c r="AJ46" s="12"/>
     </row>
     <row r="47" spans="1:36" ht="21" customHeight="1" thickBot="1">
-      <c r="A47" s="353" t="s">
+      <c r="A47" s="349" t="s">
         <v>90</v>
       </c>
-      <c r="B47" s="354"/>
-      <c r="C47" s="354"/>
-      <c r="D47" s="354"/>
-      <c r="E47" s="354"/>
+      <c r="B47" s="335"/>
+      <c r="C47" s="335"/>
+      <c r="D47" s="335"/>
+      <c r="E47" s="335"/>
       <c r="F47" s="300">
         <f>+F45-F35</f>
         <v>0</v>
@@ -6901,13 +6877,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="40"/>
-      <c r="N47" s="367" t="s">
+      <c r="N47" s="361" t="s">
         <v>90</v>
       </c>
-      <c r="O47" s="354"/>
-      <c r="P47" s="354"/>
-      <c r="Q47" s="354"/>
-      <c r="R47" s="354"/>
+      <c r="O47" s="335"/>
+      <c r="P47" s="335"/>
+      <c r="Q47" s="335"/>
+      <c r="R47" s="335"/>
       <c r="S47" s="305">
         <f>+S45-S35</f>
         <v>0</v>
@@ -14569,6 +14545,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="N47:R47"/>
     <mergeCell ref="N37:O37"/>
     <mergeCell ref="N45:Q45"/>
     <mergeCell ref="A16:B16"/>
@@ -14585,38 +14593,6 @@
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="P3:S3"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="N47:R47"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="21" orientation="portrait"/>
@@ -14625,7 +14601,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:X165"/>
+  <dimension ref="A1:T165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16.25" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="15.6640625" style="93" customWidth="1"/>
@@ -14647,13 +14623,10 @@
     <col min="18" max="18" width="15.83203125" style="93" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="15.6640625" style="93" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15.83203125" style="313" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" style="332" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.33203125" style="332" customWidth="1"/>
-    <col min="23" max="24" width="17.33203125" style="332" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.6640625" style="94"/>
+    <col min="21" max="16384" width="8.6640625" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.25" customHeight="1" thickBot="1">
+    <row r="1" spans="1:20" ht="16.25" customHeight="1" thickBot="1">
       <c r="L1" s="314">
         <f>SUBTOTAL(9,L4:L163)</f>
         <v>3764223.4018999999</v>
@@ -14671,7 +14644,7 @@
       </c>
       <c r="S1" s="316"/>
     </row>
-    <row r="2" spans="1:24" ht="16.25" customHeight="1" thickBot="1">
+    <row r="2" spans="1:20" ht="16.25" customHeight="1" thickBot="1">
       <c r="A2" s="95"/>
       <c r="B2" s="95">
         <v>1</v>
@@ -14724,12 +14697,8 @@
       </c>
       <c r="S2" s="100"/>
       <c r="T2" s="317"/>
-      <c r="U2" s="333"/>
-      <c r="V2" s="333"/>
-      <c r="W2" s="333"/>
-      <c r="X2" s="333"/>
-    </row>
-    <row r="3" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="3" spans="1:20" ht="16.25" customHeight="1">
       <c r="A3" s="101"/>
       <c r="B3" s="101" t="s">
         <v>92</v>
@@ -14788,20 +14757,8 @@
       <c r="T3" s="319" t="s">
         <v>110</v>
       </c>
-      <c r="U3" s="334" t="s">
-        <v>357</v>
-      </c>
-      <c r="V3" s="334" t="s">
-        <v>358</v>
-      </c>
-      <c r="W3" s="334" t="s">
-        <v>359</v>
-      </c>
-      <c r="X3" s="334" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="4" spans="1:20" ht="16.25" customHeight="1">
       <c r="A4" s="111">
         <v>1</v>
       </c>
@@ -14863,24 +14820,8 @@
         <v>117</v>
       </c>
       <c r="T4" s="323"/>
-      <c r="U4" s="335">
-        <f>COUNTIFS($K$4:$K$1000,K4,$F$4:$F$1000,F4)</f>
-        <v>3</v>
-      </c>
-      <c r="V4" s="335">
-        <f>AVERAGEIFS($O$4:$O$1000,$K$4:$K$1000,K4)</f>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W4" s="335">
-        <f>IFERROR(ABS(O4-V4)/V4,0)</f>
-        <v>1.8868885725363865E-2</v>
-      </c>
-      <c r="X4" s="335">
-        <f>LN(1+U4) + W4</f>
-        <v>1.4051632468452544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="5" spans="1:20" ht="16.25" customHeight="1">
       <c r="A5" s="111">
         <v>2</v>
       </c>
@@ -14943,24 +14884,8 @@
         <v>117</v>
       </c>
       <c r="T5" s="323"/>
-      <c r="U5" s="335">
-        <f t="shared" ref="U5:U68" si="3">COUNTIFS($K$4:$K$1000,K5,$F$4:$F$1000,F5)</f>
-        <v>14</v>
-      </c>
-      <c r="V5" s="335">
-        <f t="shared" ref="V5:V68" si="4">AVERAGEIFS($O$4:$O$1000,$K$4:$K$1000,K5)</f>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W5" s="335">
-        <f t="shared" ref="W5:W68" si="5">IFERROR(ABS(O5-V5)/V5,0)</f>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X5" s="335">
-        <f t="shared" ref="X5:X68" si="6">LN(1+U5) + W5</f>
-        <v>2.9883239389749234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="6" spans="1:20" ht="16.25" customHeight="1">
       <c r="A6" s="111">
         <v>3</v>
       </c>
@@ -15022,24 +14947,8 @@
         <v>117</v>
       </c>
       <c r="T6" s="323"/>
-      <c r="U6" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V6" s="335">
-        <f t="shared" si="4"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W6" s="335">
-        <f t="shared" si="5"/>
-        <v>1.8868885725363865E-2</v>
-      </c>
-      <c r="X6" s="335">
-        <f t="shared" si="6"/>
-        <v>1.4051632468452544</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="7" spans="1:20" ht="16.25" customHeight="1">
       <c r="A7" s="111">
         <v>4</v>
       </c>
@@ -15102,24 +15011,8 @@
         <v>117</v>
       </c>
       <c r="T7" s="323"/>
-      <c r="U7" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V7" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W7" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X7" s="335">
-        <f t="shared" si="6"/>
-        <v>2.9883239389749234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="8" spans="1:20" ht="16.25" customHeight="1">
       <c r="A8" s="111">
         <v>5</v>
       </c>
@@ -15181,24 +15074,8 @@
         <v>117</v>
       </c>
       <c r="T8" s="323"/>
-      <c r="U8" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V8" s="335">
-        <f t="shared" si="4"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W8" s="335">
-        <f t="shared" si="5"/>
-        <v>0.15095108580291119</v>
-      </c>
-      <c r="X8" s="335">
-        <f t="shared" si="6"/>
-        <v>1.5372454469228019</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="9" spans="1:20" ht="16.25" customHeight="1">
       <c r="A9" s="111">
         <v>6</v>
       </c>
@@ -15261,24 +15138,8 @@
         <v>117</v>
       </c>
       <c r="T9" s="323"/>
-      <c r="U9" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V9" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W9" s="335">
-        <f t="shared" si="5"/>
-        <v>0.40023411261277875</v>
-      </c>
-      <c r="X9" s="335">
-        <f t="shared" si="6"/>
-        <v>3.1082843137149889</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="10" spans="1:20" ht="16.25" customHeight="1">
       <c r="A10" s="111">
         <v>7</v>
       </c>
@@ -15340,24 +15201,8 @@
         <v>117</v>
       </c>
       <c r="T10" s="323"/>
-      <c r="U10" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V10" s="335">
-        <f t="shared" si="4"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W10" s="335">
-        <f t="shared" si="5"/>
-        <v>7.4636263653231867E-3</v>
-      </c>
-      <c r="X10" s="335">
-        <f t="shared" si="6"/>
-        <v>1.3937579874852137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="11" spans="1:20" ht="16.25" customHeight="1">
       <c r="A11" s="111">
         <v>8</v>
       </c>
@@ -15420,24 +15265,8 @@
         <v>117</v>
       </c>
       <c r="T11" s="323"/>
-      <c r="U11" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V11" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W11" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X11" s="335">
-        <f t="shared" si="6"/>
-        <v>2.9883239389749234</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="12" spans="1:20" ht="16.25" customHeight="1">
       <c r="A12" s="111">
         <v>9</v>
       </c>
@@ -15499,24 +15328,8 @@
         <v>117</v>
       </c>
       <c r="T12" s="323"/>
-      <c r="U12" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V12" s="335">
-        <f t="shared" si="4"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W12" s="335">
-        <f t="shared" si="5"/>
-        <v>7.4636263653231867E-3</v>
-      </c>
-      <c r="X12" s="335">
-        <f t="shared" si="6"/>
-        <v>1.3937579874852137</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="13" spans="1:20" ht="16.25" customHeight="1">
       <c r="A13" s="111">
         <v>10</v>
       </c>
@@ -15579,24 +15392,8 @@
         <v>117</v>
       </c>
       <c r="T13" s="323"/>
-      <c r="U13" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V13" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W13" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X13" s="335">
-        <f t="shared" si="6"/>
-        <v>2.9883239389749234</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="14" spans="1:20" ht="16.25" customHeight="1">
       <c r="A14" s="111">
         <v>11</v>
       </c>
@@ -15658,24 +15455,8 @@
         <v>117</v>
       </c>
       <c r="T14" s="323"/>
-      <c r="U14" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V14" s="335">
-        <f t="shared" si="4"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W14" s="335">
-        <f t="shared" si="5"/>
-        <v>5.9709010922584779E-2</v>
-      </c>
-      <c r="X14" s="335">
-        <f t="shared" si="6"/>
-        <v>1.4460033720424754</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="15" spans="1:20" ht="16.25" customHeight="1">
       <c r="A15" s="111">
         <v>12</v>
       </c>
@@ -15738,24 +15519,8 @@
         <v>117</v>
       </c>
       <c r="T15" s="323"/>
-      <c r="U15" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V15" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W15" s="335">
-        <f t="shared" si="5"/>
-        <v>0.3282614864000501</v>
-      </c>
-      <c r="X15" s="335">
-        <f t="shared" si="6"/>
-        <v>3.03631168750226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="16" spans="1:20" ht="16.25" customHeight="1">
       <c r="A16" s="111">
         <v>13</v>
       </c>
@@ -15817,24 +15582,8 @@
         <v>117</v>
       </c>
       <c r="T16" s="323"/>
-      <c r="U16" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V16" s="335">
-        <f t="shared" si="4"/>
-        <v>177.77833333333334</v>
-      </c>
-      <c r="W16" s="335">
-        <f t="shared" si="5"/>
-        <v>0.21250246092980959</v>
-      </c>
-      <c r="X16" s="335">
-        <f t="shared" si="6"/>
-        <v>1.3111147495979194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="17" spans="1:20" ht="16.25" customHeight="1">
       <c r="A17" s="111">
         <v>14</v>
       </c>
@@ -15897,24 +15646,8 @@
         <v>117</v>
       </c>
       <c r="T17" s="323"/>
-      <c r="U17" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V17" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W17" s="335">
-        <f t="shared" si="5"/>
-        <v>0.74809580825544963</v>
-      </c>
-      <c r="X17" s="335">
-        <f t="shared" si="6"/>
-        <v>3.4561460093576599</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="18" spans="1:20" ht="16.25" customHeight="1">
       <c r="A18" s="111">
         <v>15</v>
       </c>
@@ -15976,24 +15709,8 @@
         <v>117</v>
       </c>
       <c r="T18" s="323"/>
-      <c r="U18" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V18" s="335">
-        <f t="shared" si="4"/>
-        <v>177.77833333333334</v>
-      </c>
-      <c r="W18" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28748347661413559</v>
-      </c>
-      <c r="X18" s="335">
-        <f t="shared" si="6"/>
-        <v>1.3860957652822454</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="19" spans="1:20" ht="16.25" customHeight="1">
       <c r="A19" s="111">
         <v>16</v>
       </c>
@@ -16056,24 +15773,8 @@
         <v>117</v>
       </c>
       <c r="T19" s="323"/>
-      <c r="U19" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V19" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W19" s="335">
-        <f t="shared" si="5"/>
-        <v>0.77208068594084145</v>
-      </c>
-      <c r="X19" s="335">
-        <f t="shared" si="6"/>
-        <v>3.4801308870430514</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="20" spans="1:20" ht="16.25" customHeight="1">
       <c r="A20" s="111">
         <v>17</v>
       </c>
@@ -16135,24 +15836,8 @@
         <v>117</v>
       </c>
       <c r="T20" s="323"/>
-      <c r="U20" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V20" s="335">
-        <f t="shared" si="4"/>
-        <v>341.66666666666669</v>
-      </c>
-      <c r="W20" s="335">
-        <f t="shared" si="5"/>
-        <v>0.30487804878048785</v>
-      </c>
-      <c r="X20" s="335">
-        <f t="shared" si="6"/>
-        <v>1.4034903374485976</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="21" spans="1:20" ht="16.25" customHeight="1">
       <c r="A21" s="111">
         <v>18</v>
       </c>
@@ -16215,24 +15900,8 @@
         <v>117</v>
       </c>
       <c r="T21" s="323"/>
-      <c r="U21" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V21" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W21" s="335">
-        <f t="shared" si="5"/>
-        <v>0.57266253186192351</v>
-      </c>
-      <c r="X21" s="335">
-        <f t="shared" si="6"/>
-        <v>3.2807127329641337</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="22" spans="1:20" ht="16.25" customHeight="1">
       <c r="A22" s="111">
         <v>19</v>
       </c>
@@ -16294,24 +15963,8 @@
         <v>117</v>
       </c>
       <c r="T22" s="323"/>
-      <c r="U22" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V22" s="335">
-        <f t="shared" si="4"/>
-        <v>341.66666666666669</v>
-      </c>
-      <c r="W22" s="335">
-        <f t="shared" si="5"/>
-        <v>8.5365853658536633E-2</v>
-      </c>
-      <c r="X22" s="335">
-        <f t="shared" si="6"/>
-        <v>1.1839781423266464</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="23" spans="1:20" ht="16.25" customHeight="1">
       <c r="A23" s="111">
         <v>20</v>
       </c>
@@ -16374,24 +16027,8 @@
         <v>117</v>
       </c>
       <c r="T23" s="323"/>
-      <c r="U23" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V23" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W23" s="335">
-        <f t="shared" si="5"/>
-        <v>0.43771385771305732</v>
-      </c>
-      <c r="X23" s="335">
-        <f t="shared" si="6"/>
-        <v>3.1457640588152675</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="24" spans="1:20" ht="16.25" customHeight="1">
       <c r="A24" s="111">
         <v>21</v>
       </c>
@@ -16453,24 +16090,8 @@
         <v>117</v>
       </c>
       <c r="T24" s="323"/>
-      <c r="U24" s="335">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="V24" s="335">
-        <f t="shared" si="4"/>
-        <v>388.89107644305773</v>
-      </c>
-      <c r="W24" s="335">
-        <f t="shared" si="5"/>
-        <v>0.20000182125117696</v>
-      </c>
-      <c r="X24" s="335">
-        <f t="shared" si="6"/>
-        <v>0.89314900181112222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="25" spans="1:20" ht="16.25" customHeight="1">
       <c r="A25" s="111">
         <v>22</v>
       </c>
@@ -16533,24 +16154,8 @@
         <v>117</v>
       </c>
       <c r="T25" s="323"/>
-      <c r="U25" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V25" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W25" s="335">
-        <f t="shared" si="5"/>
-        <v>0.16031336313264791</v>
-      </c>
-      <c r="X25" s="335">
-        <f t="shared" si="6"/>
-        <v>2.8683635642348579</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="26" spans="1:20" ht="16.25" customHeight="1">
       <c r="A26" s="111">
         <v>23</v>
       </c>
@@ -16612,24 +16217,8 @@
         <v>117</v>
       </c>
       <c r="T26" s="323"/>
-      <c r="U26" s="335">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="V26" s="335">
-        <f t="shared" si="4"/>
-        <v>650</v>
-      </c>
-      <c r="W26" s="335">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="335">
-        <f t="shared" si="6"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="27" spans="1:20" ht="16.25" customHeight="1">
       <c r="A27" s="111">
         <v>24</v>
       </c>
@@ -16692,24 +16281,8 @@
         <v>117</v>
       </c>
       <c r="T27" s="323"/>
-      <c r="U27" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V27" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W27" s="335">
-        <f t="shared" si="5"/>
-        <v>0.16955517595684083</v>
-      </c>
-      <c r="X27" s="335">
-        <f t="shared" si="6"/>
-        <v>2.8776053770590511</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="28" spans="1:20" ht="16.25" customHeight="1">
       <c r="A28" s="111">
         <v>25</v>
       </c>
@@ -16771,24 +16344,8 @@
         <v>117</v>
       </c>
       <c r="T28" s="323"/>
-      <c r="U28" s="335">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="V28" s="335">
-        <f t="shared" si="4"/>
-        <v>650</v>
-      </c>
-      <c r="W28" s="335">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="335">
-        <f t="shared" si="6"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="29" spans="1:20" ht="16.25" customHeight="1">
       <c r="A29" s="111">
         <v>26</v>
       </c>
@@ -16851,24 +16408,8 @@
         <v>117</v>
       </c>
       <c r="T29" s="323"/>
-      <c r="U29" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V29" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W29" s="335">
-        <f t="shared" si="5"/>
-        <v>0.16955517595684083</v>
-      </c>
-      <c r="X29" s="335">
-        <f t="shared" si="6"/>
-        <v>2.8776053770590511</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="30" spans="1:20" ht="16.25" customHeight="1">
       <c r="A30" s="111">
         <v>27</v>
       </c>
@@ -16932,24 +16473,8 @@
       <c r="T30" s="323">
         <v>45351</v>
       </c>
-      <c r="U30" s="335">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="V30" s="335">
-        <f t="shared" si="4"/>
-        <v>1810</v>
-      </c>
-      <c r="W30" s="335">
-        <f t="shared" si="5"/>
-        <v>0.90607734806629836</v>
-      </c>
-      <c r="X30" s="335">
-        <f t="shared" si="6"/>
-        <v>1.5992245286262436</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="31" spans="1:20" ht="16.25" customHeight="1">
       <c r="A31" s="111">
         <v>28</v>
       </c>
@@ -17014,24 +16539,8 @@
       <c r="T31" s="323">
         <v>45351</v>
       </c>
-      <c r="U31" s="335">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V31" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W31" s="335">
-        <f t="shared" si="5"/>
-        <v>0.69411633859590316</v>
-      </c>
-      <c r="X31" s="335">
-        <f t="shared" si="6"/>
-        <v>3.4021665396981131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="32" spans="1:20" ht="16.25" customHeight="1">
       <c r="A32" s="111">
         <v>29</v>
       </c>
@@ -17093,24 +16602,8 @@
         <v>117</v>
       </c>
       <c r="T32" s="323"/>
-      <c r="U32" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V32" s="335">
-        <f t="shared" si="4"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W32" s="335">
-        <f t="shared" si="5"/>
-        <v>1.3305970001901675</v>
-      </c>
-      <c r="X32" s="335">
-        <f t="shared" si="6"/>
-        <v>2.9400349126242675</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="33" spans="1:20" ht="16.25" customHeight="1">
       <c r="A33" s="111">
         <v>30</v>
       </c>
@@ -17172,24 +16665,8 @@
         <v>117</v>
       </c>
       <c r="T33" s="323"/>
-      <c r="U33" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V33" s="335">
-        <f t="shared" si="4"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W33" s="335">
-        <f t="shared" si="5"/>
-        <v>1.3556550618971657E-2</v>
-      </c>
-      <c r="X33" s="335">
-        <f t="shared" si="6"/>
-        <v>1.6229944630530719</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="34" spans="1:20" ht="16.25" customHeight="1">
       <c r="A34" s="111">
         <v>31</v>
       </c>
@@ -17251,24 +16728,8 @@
         <v>117</v>
       </c>
       <c r="T34" s="323"/>
-      <c r="U34" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V34" s="335">
-        <f t="shared" si="4"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W34" s="335">
-        <f t="shared" si="5"/>
-        <v>0.67975710732037797</v>
-      </c>
-      <c r="X34" s="335">
-        <f t="shared" si="6"/>
-        <v>2.2891950197544784</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="35" spans="1:20" ht="16.25" customHeight="1">
       <c r="A35" s="111">
         <v>32</v>
       </c>
@@ -17330,24 +16791,8 @@
         <v>188</v>
       </c>
       <c r="T35" s="323"/>
-      <c r="U35" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V35" s="335">
-        <f t="shared" si="4"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W35" s="335">
-        <f t="shared" si="5"/>
-        <v>0.90289567598707665</v>
-      </c>
-      <c r="X35" s="335">
-        <f t="shared" si="6"/>
-        <v>2.512333588421177</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="36" spans="1:20" ht="16.25" customHeight="1">
       <c r="A36" s="111">
         <v>33</v>
       </c>
@@ -17367,7 +16812,7 @@
         <v>45351</v>
       </c>
       <c r="G36" s="111" t="str">
-        <f t="shared" ref="G36:G67" si="7">TEXT(F36,"yyyymm")</f>
+        <f t="shared" ref="G36:G67" si="3">TEXT(F36,"yyyymm")</f>
         <v>yyyy02</v>
       </c>
       <c r="H36" s="120" t="s">
@@ -17392,7 +16837,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O36" s="315">
-        <f t="shared" ref="O36:O67" si="8">L36/N36</f>
+        <f t="shared" ref="O36:O67" si="4">L36/N36</f>
         <v>3500</v>
       </c>
       <c r="P36" s="114">
@@ -17402,31 +16847,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R36" s="322">
-        <f t="shared" ref="R36:R67" si="9">O36*P36*Q36</f>
+        <f t="shared" ref="R36:R67" si="5">O36*P36*Q36</f>
         <v>806.75</v>
       </c>
       <c r="S36" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T36" s="323"/>
-      <c r="U36" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V36" s="335">
-        <f t="shared" si="4"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W36" s="335">
-        <f t="shared" si="5"/>
-        <v>1.2305012327485951</v>
-      </c>
-      <c r="X36" s="335">
-        <f t="shared" si="6"/>
-        <v>2.8399391451826954</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="37" spans="1:20" ht="16.25" customHeight="1">
       <c r="A37" s="111">
         <v>34</v>
       </c>
@@ -17446,7 +16875,7 @@
         <v>45351</v>
       </c>
       <c r="G37" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H37" s="120" t="s">
@@ -17471,7 +16900,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O37" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>866.05423030388613</v>
       </c>
       <c r="P37" s="114">
@@ -17481,31 +16910,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R37" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>199.62550008504576</v>
       </c>
       <c r="S37" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T37" s="323"/>
-      <c r="U37" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V37" s="335">
-        <f t="shared" si="4"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W37" s="335">
-        <f t="shared" si="5"/>
-        <v>0.44807570619429893</v>
-      </c>
-      <c r="X37" s="335">
-        <f t="shared" si="6"/>
-        <v>2.0575136186283993</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="38" spans="1:20" ht="16.25" customHeight="1">
       <c r="A38" s="111">
         <v>35</v>
       </c>
@@ -17525,7 +16938,7 @@
         <v>45351</v>
       </c>
       <c r="G38" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H38" s="120" t="s">
@@ -17550,7 +16963,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O38" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>1564.7178888115097</v>
       </c>
       <c r="P38" s="114">
@@ -17560,31 +16973,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R38" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>360.66747337105301</v>
       </c>
       <c r="S38" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T38" s="323"/>
-      <c r="U38" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V38" s="335">
-        <f t="shared" si="4"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W38" s="335">
-        <f t="shared" si="5"/>
-        <v>2.8270914577566844E-3</v>
-      </c>
-      <c r="X38" s="335">
-        <f t="shared" si="6"/>
-        <v>1.6122650038918569</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="39" spans="1:20" ht="16.25" customHeight="1">
       <c r="A39" s="111">
         <v>36</v>
       </c>
@@ -17604,7 +17001,7 @@
         <v>45351</v>
       </c>
       <c r="G39" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H39" s="120" t="s">
@@ -17629,7 +17026,7 @@
         <v>1</v>
       </c>
       <c r="O39" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>83.33</v>
       </c>
       <c r="P39" s="114">
@@ -17639,31 +17036,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R39" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>19.207564999999999</v>
       </c>
       <c r="S39" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T39" s="323"/>
-      <c r="U39" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V39" s="335">
-        <f t="shared" si="4"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W39" s="335">
-        <f t="shared" si="5"/>
-        <v>0.94689495207858854</v>
-      </c>
-      <c r="X39" s="335">
-        <f t="shared" si="6"/>
-        <v>2.5563328645126888</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="40" spans="1:20" ht="16.25" customHeight="1">
       <c r="A40" s="111">
         <v>37</v>
       </c>
@@ -17683,7 +17064,7 @@
         <v>45351</v>
       </c>
       <c r="G40" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H40" s="120" t="s">
@@ -17708,7 +17089,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O40" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="P40" s="114">
@@ -17718,31 +17099,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R40" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>691.5</v>
       </c>
       <c r="S40" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T40" s="323"/>
-      <c r="U40" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V40" s="335">
-        <f t="shared" si="4"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W40" s="335">
-        <f t="shared" si="5"/>
-        <v>1.1906706694611924</v>
-      </c>
-      <c r="X40" s="335">
-        <f t="shared" si="6"/>
-        <v>2.8001085818952927</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="41" spans="1:20" ht="16.25" customHeight="1">
       <c r="A41" s="111">
         <v>38</v>
       </c>
@@ -17762,7 +17127,7 @@
         <v>45351</v>
       </c>
       <c r="G41" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H41" s="120" t="s">
@@ -17787,7 +17152,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O41" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>672.2535839561998</v>
       </c>
       <c r="P41" s="114">
@@ -17797,31 +17162,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R41" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>154.95445110190406</v>
       </c>
       <c r="S41" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T41" s="323"/>
-      <c r="U41" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V41" s="335">
-        <f t="shared" si="4"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W41" s="335">
-        <f t="shared" si="5"/>
-        <v>0.50910459706232869</v>
-      </c>
-      <c r="X41" s="335">
-        <f t="shared" si="6"/>
-        <v>2.1185425094964287</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="42" spans="1:20" ht="16.25" customHeight="1">
       <c r="A42" s="111">
         <v>39</v>
       </c>
@@ -17841,7 +17190,7 @@
         <v>45351</v>
       </c>
       <c r="G42" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H42" s="120" t="s">
@@ -17866,7 +17215,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O42" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>1404.0969585714879</v>
       </c>
       <c r="P42" s="114">
@@ -17876,31 +17225,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R42" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>323.64434895072799</v>
       </c>
       <c r="S42" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T42" s="323"/>
-      <c r="U42" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V42" s="335">
-        <f t="shared" si="4"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W42" s="335">
-        <f t="shared" si="5"/>
-        <v>2.5304674740741797E-2</v>
-      </c>
-      <c r="X42" s="335">
-        <f t="shared" si="6"/>
-        <v>1.634742587174842</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="43" spans="1:20" ht="16.25" customHeight="1">
       <c r="A43" s="111">
         <v>40</v>
       </c>
@@ -17920,7 +17253,7 @@
         <v>45351</v>
       </c>
       <c r="G43" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H43" s="120" t="s">
@@ -17945,7 +17278,7 @@
         <v>1</v>
       </c>
       <c r="O43" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>83.33</v>
       </c>
       <c r="P43" s="114">
@@ -17955,31 +17288,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R43" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>19.207564999999999</v>
       </c>
       <c r="S43" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T43" s="323"/>
-      <c r="U43" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V43" s="335">
-        <f t="shared" si="4"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W43" s="335">
-        <f t="shared" si="5"/>
-        <v>0.93915047103793303</v>
-      </c>
-      <c r="X43" s="335">
-        <f t="shared" si="6"/>
-        <v>2.5485883834720333</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="44" spans="1:20" ht="16.25" customHeight="1">
       <c r="A44" s="111">
         <v>41</v>
       </c>
@@ -17999,7 +17316,7 @@
         <v>45351</v>
       </c>
       <c r="G44" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H44" s="120" t="s">
@@ -18024,7 +17341,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O44" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>2000</v>
       </c>
       <c r="P44" s="114">
@@ -18034,31 +17351,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R44" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>645.4</v>
       </c>
       <c r="S44" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T44" s="323"/>
-      <c r="U44" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V44" s="335">
-        <f t="shared" si="4"/>
-        <v>1218.5390520501373</v>
-      </c>
-      <c r="W44" s="335">
-        <f t="shared" si="5"/>
-        <v>0.64130972793616225</v>
-      </c>
-      <c r="X44" s="335">
-        <f t="shared" si="6"/>
-        <v>2.2507476403702626</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="45" spans="1:20" ht="16.25" customHeight="1">
       <c r="A45" s="111">
         <v>42</v>
       </c>
@@ -18078,7 +17379,7 @@
         <v>45351</v>
       </c>
       <c r="G45" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H45" s="120" t="s">
@@ -18103,7 +17404,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O45" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>335.07992695693474</v>
       </c>
       <c r="P45" s="114">
@@ -18113,31 +17414,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R45" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>108.13029242900284</v>
       </c>
       <c r="S45" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T45" s="323"/>
-      <c r="U45" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V45" s="335">
-        <f t="shared" si="4"/>
-        <v>1218.5390520501373</v>
-      </c>
-      <c r="W45" s="335">
-        <f t="shared" si="5"/>
-        <v>0.72501502812472218</v>
-      </c>
-      <c r="X45" s="335">
-        <f t="shared" si="6"/>
-        <v>2.3344529405588226</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="46" spans="1:20" ht="16.25" customHeight="1">
       <c r="A46" s="111">
         <v>43</v>
       </c>
@@ -18157,7 +17442,7 @@
         <v>45351</v>
       </c>
       <c r="G46" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H46" s="120" t="s">
@@ -18182,7 +17467,7 @@
         <v>31.159700000000001</v>
       </c>
       <c r="O46" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>892.82438534388962</v>
       </c>
       <c r="P46" s="114">
@@ -18192,31 +17477,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R46" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>288.11442915047314</v>
       </c>
       <c r="S46" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T46" s="323"/>
-      <c r="U46" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V46" s="335">
-        <f t="shared" si="4"/>
-        <v>1218.5390520501373</v>
-      </c>
-      <c r="W46" s="335">
-        <f t="shared" si="5"/>
-        <v>0.2672993254982246</v>
-      </c>
-      <c r="X46" s="335">
-        <f t="shared" si="6"/>
-        <v>1.8767372379323248</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="47" spans="1:20" ht="16.25" customHeight="1">
       <c r="A47" s="111">
         <v>44</v>
       </c>
@@ -18236,7 +17505,7 @@
         <v>45351</v>
       </c>
       <c r="G47" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H47" s="120" t="s">
@@ -18261,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>83.33</v>
       </c>
       <c r="P47" s="114">
@@ -18271,31 +17540,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R47" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>26.890591000000001</v>
       </c>
       <c r="S47" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T47" s="323"/>
-      <c r="U47" s="335">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="V47" s="335">
-        <f t="shared" si="4"/>
-        <v>1218.5390520501373</v>
-      </c>
-      <c r="W47" s="335">
-        <f t="shared" si="5"/>
-        <v>0.93161483018553981</v>
-      </c>
-      <c r="X47" s="335">
-        <f t="shared" si="6"/>
-        <v>2.5410527426196401</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="48" spans="1:20" ht="16.25" customHeight="1">
       <c r="A48" s="111">
         <v>45</v>
       </c>
@@ -18309,7 +17562,7 @@
         <v>45351</v>
       </c>
       <c r="G48" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy02</v>
       </c>
       <c r="H48" s="120" t="s">
@@ -18326,7 +17579,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="322">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P48" s="114">
@@ -18336,31 +17589,15 @@
         <v>1</v>
       </c>
       <c r="R48" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S48" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T48" s="323"/>
-      <c r="U48" s="335">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V48" s="335" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W48" s="335">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="X48" s="335">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="49" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A49" s="111">
         <v>46</v>
       </c>
@@ -18378,7 +17615,7 @@
         <v>45382</v>
       </c>
       <c r="G49" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H49" s="120" t="s">
@@ -18403,7 +17640,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O49" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>400.00000000000006</v>
       </c>
       <c r="P49" s="114">
@@ -18413,31 +17650,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R49" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>370.08000000000004</v>
       </c>
       <c r="S49" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T49" s="323"/>
-      <c r="U49" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V49" s="335">
-        <f t="shared" si="4"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W49" s="335">
-        <f t="shared" si="5"/>
-        <v>1.8868885725364007E-2</v>
-      </c>
-      <c r="X49" s="335">
-        <f t="shared" si="6"/>
-        <v>1.4051632468452546</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="50" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A50" s="111">
         <v>47</v>
       </c>
@@ -18455,7 +17676,7 @@
         <v>45382</v>
       </c>
       <c r="G50" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H50" s="120" t="s">
@@ -18481,7 +17702,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O50" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="P50" s="114">
@@ -18491,31 +17712,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R50" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.7008000000000001</v>
       </c>
       <c r="S50" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T50" s="323"/>
-      <c r="U50" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V50" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W50" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X50" s="335">
-        <f t="shared" si="6"/>
-        <v>3.0528624601124945</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="51" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A51" s="111">
         <v>48</v>
       </c>
@@ -18533,7 +17738,7 @@
         <v>45382</v>
       </c>
       <c r="G51" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H51" s="120" t="s">
@@ -18558,7 +17763,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O51" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>400.00000000000006</v>
       </c>
       <c r="P51" s="114">
@@ -18568,31 +17773,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R51" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>370.08000000000004</v>
       </c>
       <c r="S51" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T51" s="323"/>
-      <c r="U51" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V51" s="335">
-        <f t="shared" si="4"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W51" s="335">
-        <f t="shared" si="5"/>
-        <v>1.8868885725364007E-2</v>
-      </c>
-      <c r="X51" s="335">
-        <f t="shared" si="6"/>
-        <v>1.4051632468452546</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="52" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A52" s="111">
         <v>49</v>
       </c>
@@ -18610,7 +17799,7 @@
         <v>45382</v>
       </c>
       <c r="G52" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H52" s="120" t="s">
@@ -18636,7 +17825,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O52" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="P52" s="114">
@@ -18646,31 +17835,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R52" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.7008000000000001</v>
       </c>
       <c r="S52" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T52" s="323"/>
-      <c r="U52" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V52" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W52" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X52" s="335">
-        <f t="shared" si="6"/>
-        <v>3.0528624601124945</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="53" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A53" s="111">
         <v>50</v>
       </c>
@@ -18688,7 +17861,7 @@
         <v>45382</v>
       </c>
       <c r="G53" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H53" s="120" t="s">
@@ -18713,7 +17886,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O53" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>400.00000000000006</v>
       </c>
       <c r="P53" s="114">
@@ -18723,31 +17896,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R53" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>370.08000000000004</v>
       </c>
       <c r="S53" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T53" s="323"/>
-      <c r="U53" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V53" s="335">
-        <f t="shared" si="4"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W53" s="335">
-        <f t="shared" si="5"/>
-        <v>1.8868885725364007E-2</v>
-      </c>
-      <c r="X53" s="335">
-        <f t="shared" si="6"/>
-        <v>1.4051632468452546</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="54" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A54" s="111">
         <v>51</v>
       </c>
@@ -18765,7 +17922,7 @@
         <v>45382</v>
       </c>
       <c r="G54" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H54" s="120" t="s">
@@ -18791,7 +17948,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O54" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="P54" s="114">
@@ -18801,31 +17958,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R54" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.7008000000000001</v>
       </c>
       <c r="S54" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T54" s="323"/>
-      <c r="U54" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V54" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W54" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X54" s="335">
-        <f t="shared" si="6"/>
-        <v>3.0528624601124945</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="55" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A55" s="111">
         <v>52</v>
       </c>
@@ -18843,7 +17984,7 @@
         <v>45382</v>
       </c>
       <c r="G55" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H55" s="120" t="s">
@@ -18868,7 +18009,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O55" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>400.00000000000006</v>
       </c>
       <c r="P55" s="114">
@@ -18878,31 +18019,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R55" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>370.08000000000004</v>
       </c>
       <c r="S55" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T55" s="323"/>
-      <c r="U55" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V55" s="335">
-        <f t="shared" si="4"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W55" s="335">
-        <f t="shared" si="5"/>
-        <v>7.4636263653233299E-3</v>
-      </c>
-      <c r="X55" s="335">
-        <f t="shared" si="6"/>
-        <v>1.393757987485214</v>
-      </c>
-    </row>
-    <row r="56" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="56" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A56" s="111">
         <v>53</v>
       </c>
@@ -18920,7 +18045,7 @@
         <v>45382</v>
       </c>
       <c r="G56" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H56" s="120" t="s">
@@ -18946,7 +18071,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O56" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="P56" s="114">
@@ -18956,31 +18081,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R56" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.7008000000000001</v>
       </c>
       <c r="S56" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T56" s="323"/>
-      <c r="U56" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V56" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W56" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X56" s="335">
-        <f t="shared" si="6"/>
-        <v>3.0528624601124945</v>
-      </c>
-    </row>
-    <row r="57" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="57" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A57" s="111">
         <v>54</v>
       </c>
@@ -18998,7 +18107,7 @@
         <v>45382</v>
       </c>
       <c r="G57" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H57" s="120" t="s">
@@ -19023,7 +18132,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O57" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>400.00000000000006</v>
       </c>
       <c r="P57" s="114">
@@ -19033,31 +18142,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R57" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>370.08000000000004</v>
       </c>
       <c r="S57" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T57" s="323"/>
-      <c r="U57" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V57" s="335">
-        <f t="shared" si="4"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W57" s="335">
-        <f t="shared" si="5"/>
-        <v>7.4636263653233299E-3</v>
-      </c>
-      <c r="X57" s="335">
-        <f t="shared" si="6"/>
-        <v>1.393757987485214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="58" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A58" s="111">
         <v>55</v>
       </c>
@@ -19075,7 +18168,7 @@
         <v>45382</v>
       </c>
       <c r="G58" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H58" s="120" t="s">
@@ -19101,7 +18194,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O58" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="P58" s="114">
@@ -19111,31 +18204,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R58" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.7008000000000001</v>
       </c>
       <c r="S58" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T58" s="323"/>
-      <c r="U58" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V58" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W58" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X58" s="335">
-        <f t="shared" si="6"/>
-        <v>3.0528624601124945</v>
-      </c>
-    </row>
-    <row r="59" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="59" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A59" s="111">
         <v>56</v>
       </c>
@@ -19153,7 +18230,7 @@
         <v>45382</v>
       </c>
       <c r="G59" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H59" s="120" t="s">
@@ -19178,7 +18255,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O59" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>400.00000000000006</v>
       </c>
       <c r="P59" s="114">
@@ -19188,31 +18265,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R59" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>370.08000000000004</v>
       </c>
       <c r="S59" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T59" s="323"/>
-      <c r="U59" s="335">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="V59" s="335">
-        <f t="shared" si="4"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W59" s="335">
-        <f t="shared" si="5"/>
-        <v>7.4636263653233299E-3</v>
-      </c>
-      <c r="X59" s="335">
-        <f t="shared" si="6"/>
-        <v>1.393757987485214</v>
-      </c>
-    </row>
-    <row r="60" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="60" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A60" s="111">
         <v>57</v>
       </c>
@@ -19230,7 +18291,7 @@
         <v>45382</v>
       </c>
       <c r="G60" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H60" s="120" t="s">
@@ -19256,7 +18317,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O60" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="P60" s="114">
@@ -19266,31 +18327,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R60" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.7008000000000001</v>
       </c>
       <c r="S60" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T60" s="323"/>
-      <c r="U60" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V60" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W60" s="335">
-        <f t="shared" si="5"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X60" s="335">
-        <f t="shared" si="6"/>
-        <v>3.0528624601124945</v>
-      </c>
-    </row>
-    <row r="61" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="61" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A61" s="111">
         <v>58</v>
       </c>
@@ -19308,7 +18353,7 @@
         <v>45382</v>
       </c>
       <c r="G61" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H61" s="120" t="s">
@@ -19333,7 +18378,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O61" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="P61" s="114">
@@ -19343,31 +18388,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R61" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>185.04</v>
       </c>
       <c r="S61" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T61" s="323"/>
-      <c r="U61" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V61" s="335">
-        <f t="shared" si="4"/>
-        <v>177.77833333333334</v>
-      </c>
-      <c r="W61" s="335">
-        <f t="shared" si="5"/>
-        <v>0.12499648438598628</v>
-      </c>
-      <c r="X61" s="335">
-        <f t="shared" si="6"/>
-        <v>1.2236087730540961</v>
-      </c>
-    </row>
-    <row r="62" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="62" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A62" s="111">
         <v>59</v>
       </c>
@@ -19385,7 +18414,7 @@
         <v>45382</v>
       </c>
       <c r="G62" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H62" s="120" t="s">
@@ -19411,7 +18440,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O62" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="P62" s="114">
@@ -19421,31 +18450,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R62" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>1.8504</v>
       </c>
       <c r="S62" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T62" s="323"/>
-      <c r="U62" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V62" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W62" s="335">
-        <f t="shared" si="5"/>
-        <v>0.64013686893635668</v>
-      </c>
-      <c r="X62" s="335">
-        <f t="shared" si="6"/>
-        <v>3.4127255911761378</v>
-      </c>
-    </row>
-    <row r="63" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="63" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A63" s="111">
         <v>60</v>
       </c>
@@ -19463,7 +18476,7 @@
         <v>45382</v>
       </c>
       <c r="G63" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H63" s="120" t="s">
@@ -19488,7 +18501,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O63" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="P63" s="114">
@@ -19498,31 +18511,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R63" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>185.04</v>
       </c>
       <c r="S63" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T63" s="323"/>
-      <c r="U63" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V63" s="335">
-        <f t="shared" si="4"/>
-        <v>177.77833333333334</v>
-      </c>
-      <c r="W63" s="335">
-        <f t="shared" si="5"/>
-        <v>0.12499648438598628</v>
-      </c>
-      <c r="X63" s="335">
-        <f t="shared" si="6"/>
-        <v>1.2236087730540961</v>
-      </c>
-    </row>
-    <row r="64" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="64" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A64" s="111">
         <v>61</v>
       </c>
@@ -19540,7 +18537,7 @@
         <v>45382</v>
       </c>
       <c r="G64" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H64" s="120" t="s">
@@ -19566,7 +18563,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O64" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="P64" s="114">
@@ -19576,31 +18573,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R64" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>1.8504</v>
       </c>
       <c r="S64" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T64" s="323"/>
-      <c r="U64" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V64" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W64" s="335">
-        <f t="shared" si="5"/>
-        <v>0.64013686893635668</v>
-      </c>
-      <c r="X64" s="335">
-        <f t="shared" si="6"/>
-        <v>3.4127255911761378</v>
-      </c>
-    </row>
-    <row r="65" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="65" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A65" s="111">
         <v>62</v>
       </c>
@@ -19618,7 +18599,7 @@
         <v>45382</v>
       </c>
       <c r="G65" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H65" s="120" t="s">
@@ -19643,7 +18624,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O65" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>375.00000000000006</v>
       </c>
       <c r="P65" s="114">
@@ -19653,31 +18634,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R65" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>346.95000000000005</v>
       </c>
       <c r="S65" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T65" s="323"/>
-      <c r="U65" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V65" s="335">
-        <f t="shared" si="4"/>
-        <v>341.66666666666669</v>
-      </c>
-      <c r="W65" s="335">
-        <f t="shared" si="5"/>
-        <v>9.7560975609756198E-2</v>
-      </c>
-      <c r="X65" s="335">
-        <f t="shared" si="6"/>
-        <v>1.196173264277866</v>
-      </c>
-    </row>
-    <row r="66" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="66" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A66" s="111">
         <v>63</v>
       </c>
@@ -19695,7 +18660,7 @@
         <v>45382</v>
       </c>
       <c r="G66" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H66" s="120" t="s">
@@ -19721,7 +18686,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O66" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>3.7500000000000004</v>
       </c>
       <c r="P66" s="114">
@@ -19731,31 +18696,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R66" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>3.4695000000000005</v>
       </c>
       <c r="S66" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T66" s="323"/>
-      <c r="U66" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V66" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W66" s="335">
-        <f t="shared" si="5"/>
-        <v>0.32525662925566867</v>
-      </c>
-      <c r="X66" s="335">
-        <f t="shared" si="6"/>
-        <v>3.09784535149545</v>
-      </c>
-    </row>
-    <row r="67" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="67" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A67" s="111">
         <v>64</v>
       </c>
@@ -19773,7 +18722,7 @@
         <v>45382</v>
       </c>
       <c r="G67" s="111" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>yyyy03</v>
       </c>
       <c r="H67" s="120" t="s">
@@ -19798,7 +18747,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O67" s="315">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>375.00000000000006</v>
       </c>
       <c r="P67" s="114">
@@ -19808,31 +18757,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R67" s="322">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>346.95000000000005</v>
       </c>
       <c r="S67" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T67" s="323"/>
-      <c r="U67" s="335">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="V67" s="335">
-        <f t="shared" si="4"/>
-        <v>341.66666666666669</v>
-      </c>
-      <c r="W67" s="335">
-        <f t="shared" si="5"/>
-        <v>9.7560975609756198E-2</v>
-      </c>
-      <c r="X67" s="335">
-        <f t="shared" si="6"/>
-        <v>1.196173264277866</v>
-      </c>
-    </row>
-    <row r="68" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="68" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A68" s="111">
         <v>65</v>
       </c>
@@ -19850,7 +18783,7 @@
         <v>45382</v>
       </c>
       <c r="G68" s="111" t="str">
-        <f t="shared" ref="G68:G99" si="10">TEXT(F68,"yyyymm")</f>
+        <f t="shared" ref="G68:G99" si="6">TEXT(F68,"yyyymm")</f>
         <v>yyyy03</v>
       </c>
       <c r="H68" s="120" t="s">
@@ -19876,7 +18809,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O68" s="315">
-        <f t="shared" ref="O68:O99" si="11">L68/N68</f>
+        <f t="shared" ref="O68:O99" si="7">L68/N68</f>
         <v>3.7500000000000004</v>
       </c>
       <c r="P68" s="114">
@@ -19886,31 +18819,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R68" s="322">
-        <f t="shared" ref="R68:R99" si="12">O68*P68*Q68</f>
+        <f t="shared" ref="R68:R99" si="8">O68*P68*Q68</f>
         <v>3.4695000000000005</v>
       </c>
       <c r="S68" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T68" s="323"/>
-      <c r="U68" s="335">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="V68" s="335">
-        <f t="shared" si="4"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W68" s="335">
-        <f t="shared" si="5"/>
-        <v>0.32525662925566867</v>
-      </c>
-      <c r="X68" s="335">
-        <f t="shared" si="6"/>
-        <v>3.09784535149545</v>
-      </c>
-    </row>
-    <row r="69" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="69" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A69" s="111">
         <v>66</v>
       </c>
@@ -19928,7 +18845,7 @@
         <v>45382</v>
       </c>
       <c r="G69" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H69" s="120" t="s">
@@ -19953,7 +18870,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O69" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>483.33322932917321</v>
       </c>
       <c r="P69" s="114">
@@ -19963,31 +18880,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R69" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>447.17990377535108</v>
       </c>
       <c r="S69" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T69" s="323"/>
-      <c r="U69" s="335">
-        <f t="shared" ref="U69:U132" si="13">COUNTIFS($K$4:$K$1000,K69,$F$4:$F$1000,F69)</f>
-        <v>1</v>
-      </c>
-      <c r="V69" s="335">
-        <f t="shared" ref="V69:V132" si="14">AVERAGEIFS($O$4:$O$1000,$K$4:$K$1000,K69)</f>
-        <v>388.89107644305773</v>
-      </c>
-      <c r="W69" s="335">
-        <f t="shared" ref="W69:W132" si="15">IFERROR(ABS(O69-V69)/V69,0)</f>
-        <v>0.24284988421415707</v>
-      </c>
-      <c r="X69" s="335">
-        <f t="shared" ref="X69:X132" si="16">LN(1+U69) + W69</f>
-        <v>0.93599706477410238</v>
-      </c>
-    </row>
-    <row r="70" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="70" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A70" s="111">
         <v>67</v>
       </c>
@@ -20005,7 +18906,7 @@
         <v>45382</v>
       </c>
       <c r="G70" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H70" s="120" t="s">
@@ -20031,7 +18932,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O70" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4.8333322932917318</v>
       </c>
       <c r="P70" s="114">
@@ -20041,31 +18942,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R70" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>4.4717990377535104</v>
       </c>
       <c r="S70" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T70" s="323"/>
-      <c r="U70" s="335">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="V70" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W70" s="335">
-        <f t="shared" si="15"/>
-        <v>0.13033095373250886</v>
-      </c>
-      <c r="X70" s="335">
-        <f t="shared" si="16"/>
-        <v>2.9029196759722899</v>
-      </c>
-    </row>
-    <row r="71" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="71" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A71" s="111">
         <v>68</v>
       </c>
@@ -20083,7 +18968,7 @@
         <v>45382</v>
       </c>
       <c r="G71" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H71" s="120" t="s">
@@ -20108,7 +18993,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O71" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>650.00000000000011</v>
       </c>
       <c r="P71" s="114">
@@ -20118,31 +19003,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R71" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>601.38000000000011</v>
       </c>
       <c r="S71" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T71" s="323"/>
-      <c r="U71" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V71" s="335">
-        <f t="shared" si="14"/>
-        <v>650</v>
-      </c>
-      <c r="W71" s="335">
-        <f t="shared" si="15"/>
-        <v>1.7490282726402466E-16</v>
-      </c>
-      <c r="X71" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994551</v>
-      </c>
-    </row>
-    <row r="72" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="72" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A72" s="111">
         <v>69</v>
       </c>
@@ -20160,7 +19029,7 @@
         <v>45382</v>
       </c>
       <c r="G72" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H72" s="120" t="s">
@@ -20186,7 +19055,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O72" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>6.5000000000000009</v>
       </c>
       <c r="P72" s="114">
@@ -20196,31 +19065,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R72" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>6.0138000000000007</v>
       </c>
       <c r="S72" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T72" s="323"/>
-      <c r="U72" s="335">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="V72" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W72" s="335">
-        <f t="shared" si="15"/>
-        <v>0.169555175956841</v>
-      </c>
-      <c r="X72" s="335">
-        <f t="shared" si="16"/>
-        <v>2.9421438981966221</v>
-      </c>
-    </row>
-    <row r="73" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="73" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A73" s="111">
         <v>70</v>
       </c>
@@ -20238,7 +19091,7 @@
         <v>45382</v>
       </c>
       <c r="G73" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H73" s="120" t="s">
@@ -20263,7 +19116,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O73" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>650.00000000000011</v>
       </c>
       <c r="P73" s="114">
@@ -20273,31 +19126,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R73" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>150.34500000000003</v>
       </c>
       <c r="S73" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T73" s="323"/>
-      <c r="U73" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V73" s="335">
-        <f t="shared" si="14"/>
-        <v>650</v>
-      </c>
-      <c r="W73" s="335">
-        <f t="shared" si="15"/>
-        <v>1.7490282726402466E-16</v>
-      </c>
-      <c r="X73" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994551</v>
-      </c>
-    </row>
-    <row r="74" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="74" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A74" s="111">
         <v>71</v>
       </c>
@@ -20315,7 +19152,7 @@
         <v>45382</v>
       </c>
       <c r="G74" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H74" s="120" t="s">
@@ -20341,7 +19178,7 @@
         <v>32.049999999999997</v>
       </c>
       <c r="O74" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>6.5000000000000009</v>
       </c>
       <c r="P74" s="114">
@@ -20351,31 +19188,15 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R74" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>1.5034500000000002</v>
       </c>
       <c r="S74" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T74" s="323"/>
-      <c r="U74" s="335">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="V74" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W74" s="335">
-        <f t="shared" si="15"/>
-        <v>0.169555175956841</v>
-      </c>
-      <c r="X74" s="335">
-        <f t="shared" si="16"/>
-        <v>2.9421438981966221</v>
-      </c>
-    </row>
-    <row r="75" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="75" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A75" s="111">
         <v>72</v>
       </c>
@@ -20393,7 +19214,7 @@
         <v>45382</v>
       </c>
       <c r="G75" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H75" s="120" t="s">
@@ -20418,7 +19239,7 @@
         <v>1</v>
       </c>
       <c r="O75" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1033.83</v>
       </c>
       <c r="P75" s="114">
@@ -20428,7 +19249,7 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R75" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>956.49951599999997</v>
       </c>
       <c r="S75" s="322" t="s">
@@ -20437,24 +19258,8 @@
       <c r="T75" s="323">
         <v>45361</v>
       </c>
-      <c r="U75" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V75" s="335">
-        <f t="shared" si="14"/>
-        <v>660.82333333333327</v>
-      </c>
-      <c r="W75" s="335">
-        <f t="shared" si="15"/>
-        <v>0.56445746972211441</v>
-      </c>
-      <c r="X75" s="335">
-        <f t="shared" si="16"/>
-        <v>1.2576046502820597</v>
-      </c>
-    </row>
-    <row r="76" spans="1:24" s="93" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="76" spans="1:20" s="93" customFormat="1" ht="16.25" customHeight="1">
       <c r="A76" s="111">
         <v>73</v>
       </c>
@@ -20472,7 +19277,7 @@
         <v>45382</v>
       </c>
       <c r="G76" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H76" s="120" t="s">
@@ -20497,7 +19302,7 @@
         <v>1</v>
       </c>
       <c r="O76" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>10.34</v>
       </c>
       <c r="P76" s="116">
@@ -20507,7 +19312,7 @@
         <v>0.92520000000000002</v>
       </c>
       <c r="R76" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>9.5665680000000002</v>
       </c>
       <c r="S76" s="322" t="s">
@@ -20516,24 +19321,8 @@
       <c r="T76" s="323">
         <v>45361</v>
       </c>
-      <c r="U76" s="335">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="V76" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W76" s="335">
-        <f t="shared" si="15"/>
-        <v>0.86049238759903601</v>
-      </c>
-      <c r="X76" s="335">
-        <f t="shared" si="16"/>
-        <v>3.6330811098388169</v>
-      </c>
-    </row>
-    <row r="77" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="77" spans="1:20" ht="16.25" customHeight="1">
       <c r="A77" s="111">
         <v>74</v>
       </c>
@@ -20551,7 +19340,7 @@
         <v>45382</v>
       </c>
       <c r="G77" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H77" s="120" t="s">
@@ -20576,7 +19365,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O77" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2000</v>
       </c>
       <c r="P77" s="114">
@@ -20586,31 +19375,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R77" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>461</v>
       </c>
       <c r="S77" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T77" s="323"/>
-      <c r="U77" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V77" s="335">
-        <f t="shared" si="14"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W77" s="335">
-        <f t="shared" si="15"/>
-        <v>1.3305970001901675</v>
-      </c>
-      <c r="X77" s="335">
-        <f t="shared" si="16"/>
-        <v>2.9400349126242675</v>
-      </c>
-    </row>
-    <row r="78" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="78" spans="1:20" ht="16.25" customHeight="1">
       <c r="A78" s="111">
         <v>75</v>
       </c>
@@ -20628,7 +19401,7 @@
         <v>45382</v>
       </c>
       <c r="G78" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H78" s="120" t="s">
@@ -20653,7 +19426,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O78" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>919.69806785729759</v>
       </c>
       <c r="P78" s="114">
@@ -20663,31 +19436,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R78" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>211.99040464110709</v>
       </c>
       <c r="S78" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T78" s="323"/>
-      <c r="U78" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V78" s="335">
-        <f t="shared" si="14"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W78" s="335">
-        <f t="shared" si="15"/>
-        <v>7.1722779014455382E-2</v>
-      </c>
-      <c r="X78" s="335">
-        <f t="shared" si="16"/>
-        <v>1.6811606914485557</v>
-      </c>
-    </row>
-    <row r="79" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="79" spans="1:20" ht="16.25" customHeight="1">
       <c r="A79" s="111">
         <v>76</v>
       </c>
@@ -20705,7 +19462,7 @@
         <v>45382</v>
       </c>
       <c r="G79" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H79" s="120" t="s">
@@ -20730,7 +19487,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O79" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>405.36434425467854</v>
       </c>
       <c r="P79" s="114">
@@ -20740,31 +19497,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R79" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>93.436481350703403</v>
       </c>
       <c r="S79" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T79" s="323"/>
-      <c r="U79" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V79" s="335">
-        <f t="shared" si="14"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W79" s="335">
-        <f t="shared" si="15"/>
-        <v>0.52762953764799592</v>
-      </c>
-      <c r="X79" s="335">
-        <f t="shared" si="16"/>
-        <v>2.1370674500820961</v>
-      </c>
-    </row>
-    <row r="80" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="80" spans="1:20" ht="16.25" customHeight="1">
       <c r="A80" s="111">
         <v>77</v>
       </c>
@@ -20782,7 +19523,7 @@
         <v>45382</v>
       </c>
       <c r="G80" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H80" s="120" t="s">
@@ -20807,7 +19548,7 @@
         <v>1</v>
       </c>
       <c r="O80" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>83.33</v>
       </c>
       <c r="P80" s="114">
@@ -20817,31 +19558,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R80" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>19.207564999999999</v>
       </c>
       <c r="S80" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T80" s="323"/>
-      <c r="U80" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V80" s="335">
-        <f t="shared" si="14"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W80" s="335">
-        <f t="shared" si="15"/>
-        <v>0.90289567598707665</v>
-      </c>
-      <c r="X80" s="335">
-        <f t="shared" si="16"/>
-        <v>2.512333588421177</v>
-      </c>
-    </row>
-    <row r="81" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="81" spans="1:20" ht="16.25" customHeight="1">
       <c r="A81" s="111">
         <v>78</v>
       </c>
@@ -20859,7 +19584,7 @@
         <v>45382</v>
       </c>
       <c r="G81" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H81" s="120" t="s">
@@ -20884,7 +19609,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O81" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>3499.9999999999995</v>
       </c>
       <c r="P81" s="114">
@@ -20894,31 +19619,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R81" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>806.74999999999989</v>
       </c>
       <c r="S81" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T81" s="323"/>
-      <c r="U81" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V81" s="335">
-        <f t="shared" si="14"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W81" s="335">
-        <f t="shared" si="15"/>
-        <v>1.2305012327485947</v>
-      </c>
-      <c r="X81" s="335">
-        <f t="shared" si="16"/>
-        <v>2.839939145182695</v>
-      </c>
-    </row>
-    <row r="82" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="82" spans="1:20" ht="16.25" customHeight="1">
       <c r="A82" s="111">
         <v>79</v>
       </c>
@@ -20936,7 +19645,7 @@
         <v>45382</v>
       </c>
       <c r="G82" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H82" s="120" t="s">
@@ -20961,7 +19670,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O82" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1236.3610176736233</v>
       </c>
       <c r="P82" s="114">
@@ -20971,31 +19680,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R82" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>284.98121457377022</v>
       </c>
       <c r="S82" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T82" s="323"/>
-      <c r="U82" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V82" s="335">
-        <f t="shared" si="14"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W82" s="335">
-        <f t="shared" si="15"/>
-        <v>0.21208435027333589</v>
-      </c>
-      <c r="X82" s="335">
-        <f t="shared" si="16"/>
-        <v>1.8215222627074361</v>
-      </c>
-    </row>
-    <row r="83" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="83" spans="1:20" ht="16.25" customHeight="1">
       <c r="A83" s="111">
         <v>80</v>
       </c>
@@ -21013,7 +19706,7 @@
         <v>45382</v>
       </c>
       <c r="G83" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H83" s="120" t="s">
@@ -21038,7 +19731,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O83" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1510.1606298822376</v>
       </c>
       <c r="P83" s="114">
@@ -21048,31 +19741,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R83" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>348.09202518785577</v>
       </c>
       <c r="S83" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T83" s="323"/>
-      <c r="U83" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V83" s="335">
-        <f t="shared" si="14"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W83" s="335">
-        <f t="shared" si="15"/>
-        <v>3.7595672399792647E-2</v>
-      </c>
-      <c r="X83" s="335">
-        <f t="shared" si="16"/>
-        <v>1.6470335848338928</v>
-      </c>
-    </row>
-    <row r="84" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="84" spans="1:20" ht="16.25" customHeight="1">
       <c r="A84" s="111">
         <v>81</v>
       </c>
@@ -21090,7 +19767,7 @@
         <v>45382</v>
       </c>
       <c r="G84" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H84" s="120" t="s">
@@ -21115,7 +19792,7 @@
         <v>1</v>
       </c>
       <c r="O84" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>83.33</v>
       </c>
       <c r="P84" s="114">
@@ -21125,31 +19802,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R84" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>19.207564999999999</v>
       </c>
       <c r="S84" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T84" s="323"/>
-      <c r="U84" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V84" s="335">
-        <f t="shared" si="14"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W84" s="335">
-        <f t="shared" si="15"/>
-        <v>0.94689495207858854</v>
-      </c>
-      <c r="X84" s="335">
-        <f t="shared" si="16"/>
-        <v>2.5563328645126888</v>
-      </c>
-    </row>
-    <row r="85" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="85" spans="1:20" ht="16.25" customHeight="1">
       <c r="A85" s="111">
         <v>82</v>
       </c>
@@ -21167,7 +19828,7 @@
         <v>45382</v>
       </c>
       <c r="G85" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H85" s="120" t="s">
@@ -21192,7 +19853,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O85" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2999.9999999999995</v>
       </c>
       <c r="P85" s="114">
@@ -21202,31 +19863,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R85" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>691.49999999999989</v>
       </c>
       <c r="S85" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T85" s="323"/>
-      <c r="U85" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V85" s="335">
-        <f t="shared" si="14"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W85" s="335">
-        <f t="shared" si="15"/>
-        <v>1.1906706694611919</v>
-      </c>
-      <c r="X85" s="335">
-        <f t="shared" si="16"/>
-        <v>2.8001085818952922</v>
-      </c>
-    </row>
-    <row r="86" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="86" spans="1:20" ht="16.25" customHeight="1">
       <c r="A86" s="111">
         <v>83</v>
       </c>
@@ -21244,7 +19889,7 @@
         <v>45382</v>
       </c>
       <c r="G86" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H86" s="120" t="s">
@@ -21269,7 +19914,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O86" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1012.0385685170386</v>
       </c>
       <c r="P86" s="114">
@@ -21279,31 +19924,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R86" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>233.27489004317741</v>
       </c>
       <c r="S86" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T86" s="323"/>
-      <c r="U86" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V86" s="335">
-        <f t="shared" si="14"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W86" s="335">
-        <f t="shared" si="15"/>
-        <v>0.26098559719541081</v>
-      </c>
-      <c r="X86" s="335">
-        <f t="shared" si="16"/>
-        <v>1.8704235096295112</v>
-      </c>
-    </row>
-    <row r="87" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="87" spans="1:20" ht="16.25" customHeight="1">
       <c r="A87" s="111">
         <v>84</v>
       </c>
@@ -21321,7 +19950,7 @@
         <v>45382</v>
       </c>
       <c r="G87" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H87" s="120" t="s">
@@ -21346,7 +19975,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O87" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1510.1606298822376</v>
       </c>
       <c r="P87" s="114">
@@ -21356,31 +19985,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R87" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>348.09202518785577</v>
       </c>
       <c r="S87" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T87" s="323"/>
-      <c r="U87" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V87" s="335">
-        <f t="shared" si="14"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W87" s="335">
-        <f t="shared" si="15"/>
-        <v>0.10275486601935241</v>
-      </c>
-      <c r="X87" s="335">
-        <f t="shared" si="16"/>
-        <v>1.7121927784534527</v>
-      </c>
-    </row>
-    <row r="88" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="88" spans="1:20" ht="16.25" customHeight="1">
       <c r="A88" s="111">
         <v>85</v>
       </c>
@@ -21398,7 +20011,7 @@
         <v>45382</v>
       </c>
       <c r="G88" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H88" s="120" t="s">
@@ -21423,7 +20036,7 @@
         <v>1</v>
       </c>
       <c r="O88" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>83.33</v>
       </c>
       <c r="P88" s="114">
@@ -21433,31 +20046,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R88" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>19.207564999999999</v>
       </c>
       <c r="S88" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T88" s="323"/>
-      <c r="U88" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V88" s="335">
-        <f t="shared" si="14"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W88" s="335">
-        <f t="shared" si="15"/>
-        <v>0.93915047103793303</v>
-      </c>
-      <c r="X88" s="335">
-        <f t="shared" si="16"/>
-        <v>2.5485883834720333</v>
-      </c>
-    </row>
-    <row r="89" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="89" spans="1:20" ht="16.25" customHeight="1">
       <c r="A89" s="111">
         <v>86</v>
       </c>
@@ -21475,7 +20072,7 @@
         <v>45382</v>
       </c>
       <c r="G89" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H89" s="120" t="s">
@@ -21500,7 +20097,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O89" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2000</v>
       </c>
       <c r="P89" s="114">
@@ -21510,31 +20107,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R89" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>553.20000000000005</v>
       </c>
       <c r="S89" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T89" s="323"/>
-      <c r="U89" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V89" s="335">
-        <f t="shared" si="14"/>
-        <v>1218.5390520501373</v>
-      </c>
-      <c r="W89" s="335">
-        <f t="shared" si="15"/>
-        <v>0.64130972793616225</v>
-      </c>
-      <c r="X89" s="335">
-        <f t="shared" si="16"/>
-        <v>1.3344569084961075</v>
-      </c>
-    </row>
-    <row r="90" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="90" spans="1:20" ht="16.25" customHeight="1">
       <c r="A90" s="111">
         <v>87</v>
       </c>
@@ -21552,7 +20133,7 @@
         <v>45382</v>
       </c>
       <c r="G90" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H90" s="120" t="s">
@@ -21578,7 +20159,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O90" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="P90" s="114">
@@ -21588,31 +20169,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R90" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>5.532</v>
       </c>
       <c r="S90" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T90" s="323"/>
-      <c r="U90" s="335">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="V90" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W90" s="335">
-        <f t="shared" si="15"/>
-        <v>2.5986313106364332</v>
-      </c>
-      <c r="X90" s="335">
-        <f t="shared" si="16"/>
-        <v>5.3712200328762147</v>
-      </c>
-    </row>
-    <row r="91" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="91" spans="1:20" ht="16.25" customHeight="1">
       <c r="A91" s="111">
         <v>88</v>
       </c>
@@ -21630,7 +20195,7 @@
         <v>45382</v>
       </c>
       <c r="G91" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H91" s="120" t="s">
@@ -21655,7 +20220,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O91" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>2799.9999999999995</v>
       </c>
       <c r="P91" s="114">
@@ -21665,31 +20230,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R91" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>1290.8</v>
       </c>
       <c r="S91" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T91" s="323"/>
-      <c r="U91" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V91" s="335">
-        <f t="shared" si="14"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W91" s="335">
-        <f t="shared" si="15"/>
-        <v>1.219098746200652</v>
-      </c>
-      <c r="X91" s="335">
-        <f t="shared" si="16"/>
-        <v>2.8285366586347522</v>
-      </c>
-    </row>
-    <row r="92" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="92" spans="1:20" ht="16.25" customHeight="1">
       <c r="A92" s="111">
         <v>89</v>
       </c>
@@ -21707,7 +20256,7 @@
         <v>45382</v>
       </c>
       <c r="G92" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H92" s="120" t="s">
@@ -21732,7 +20281,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O92" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>1294.699771413704</v>
       </c>
       <c r="P92" s="114">
@@ -21742,31 +20291,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R92" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>596.85659462171759</v>
       </c>
       <c r="S92" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T92" s="323"/>
-      <c r="U92" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V92" s="335">
-        <f t="shared" si="14"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W92" s="335">
-        <f t="shared" si="15"/>
-        <v>2.6095228375150603E-2</v>
-      </c>
-      <c r="X92" s="335">
-        <f t="shared" si="16"/>
-        <v>1.6355331408092508</v>
-      </c>
-    </row>
-    <row r="93" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="93" spans="1:20" ht="16.25" customHeight="1">
       <c r="A93" s="111">
         <v>90</v>
       </c>
@@ -21784,7 +20317,7 @@
         <v>45382</v>
       </c>
       <c r="G93" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H93" s="120" t="s">
@@ -21809,7 +20342,7 @@
         <v>32.285400000000003</v>
       </c>
       <c r="O93" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>586.13800665316205</v>
       </c>
       <c r="P93" s="114">
@@ -21819,31 +20352,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R93" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>270.20962106710772</v>
       </c>
       <c r="S93" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T93" s="323"/>
-      <c r="U93" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V93" s="335">
-        <f t="shared" si="14"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W93" s="335">
-        <f t="shared" si="15"/>
-        <v>0.5354649586912209</v>
-      </c>
-      <c r="X93" s="335">
-        <f t="shared" si="16"/>
-        <v>2.1449028711253213</v>
-      </c>
-    </row>
-    <row r="94" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="94" spans="1:20" ht="16.25" customHeight="1">
       <c r="A94" s="111">
         <v>91</v>
       </c>
@@ -21861,7 +20378,7 @@
         <v>45382</v>
       </c>
       <c r="G94" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H94" s="120" t="s">
@@ -21886,7 +20403,7 @@
         <v>1</v>
       </c>
       <c r="O94" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>83.33</v>
       </c>
       <c r="P94" s="114">
@@ -21896,31 +20413,15 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="R94" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>38.415129999999998</v>
       </c>
       <c r="S94" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T94" s="323"/>
-      <c r="U94" s="335">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="V94" s="335">
-        <f t="shared" si="14"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W94" s="335">
-        <f t="shared" si="15"/>
-        <v>0.93395803624253559</v>
-      </c>
-      <c r="X94" s="335">
-        <f t="shared" si="16"/>
-        <v>2.5433959486766358</v>
-      </c>
-    </row>
-    <row r="95" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="95" spans="1:20" ht="16.25" customHeight="1">
       <c r="A95" s="111">
         <v>92</v>
       </c>
@@ -21934,7 +20435,7 @@
         <v>45382</v>
       </c>
       <c r="G95" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy03</v>
       </c>
       <c r="H95" s="120" t="s">
@@ -21961,31 +20462,15 @@
         <v>1</v>
       </c>
       <c r="R95" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S95" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T95" s="323"/>
-      <c r="U95" s="335">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V95" s="335" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W95" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X95" s="335">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="96" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A96" s="111">
         <v>93</v>
       </c>
@@ -22003,7 +20488,7 @@
         <v>45412</v>
       </c>
       <c r="G96" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy04</v>
       </c>
       <c r="H96" s="120" t="s">
@@ -22028,7 +20513,7 @@
         <v>1</v>
       </c>
       <c r="O96" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>400</v>
       </c>
       <c r="P96" s="114">
@@ -22038,31 +20523,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R96" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>368.49200000000002</v>
       </c>
       <c r="S96" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T96" s="323"/>
-      <c r="U96" s="335">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="V96" s="335">
-        <f t="shared" si="14"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W96" s="335">
-        <f t="shared" si="15"/>
-        <v>1.8868885725363865E-2</v>
-      </c>
-      <c r="X96" s="335">
-        <f t="shared" si="16"/>
-        <v>1.4051632468452544</v>
-      </c>
-    </row>
-    <row r="97" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="97" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A97" s="111">
         <v>94</v>
       </c>
@@ -22080,7 +20549,7 @@
         <v>45412</v>
       </c>
       <c r="G97" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy04</v>
       </c>
       <c r="H97" s="120" t="s">
@@ -22106,7 +20575,7 @@
         <v>1</v>
       </c>
       <c r="O97" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="P97" s="114">
@@ -22116,31 +20585,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R97" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>3.68492</v>
       </c>
       <c r="S97" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T97" s="323"/>
-      <c r="U97" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V97" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W97" s="335">
-        <f t="shared" si="15"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X97" s="335">
-        <f t="shared" si="16"/>
-        <v>3.4991495627409139</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="98" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A98" s="111">
         <v>95</v>
       </c>
@@ -22158,7 +20611,7 @@
         <v>45412</v>
       </c>
       <c r="G98" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy04</v>
       </c>
       <c r="H98" s="120" t="s">
@@ -22183,7 +20636,7 @@
         <v>1</v>
       </c>
       <c r="O98" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>400</v>
       </c>
       <c r="P98" s="114">
@@ -22193,31 +20646,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R98" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>368.49200000000002</v>
       </c>
       <c r="S98" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T98" s="323"/>
-      <c r="U98" s="335">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="V98" s="335">
-        <f t="shared" si="14"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W98" s="335">
-        <f t="shared" si="15"/>
-        <v>1.8868885725363865E-2</v>
-      </c>
-      <c r="X98" s="335">
-        <f t="shared" si="16"/>
-        <v>1.4051632468452544</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="99" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A99" s="111">
         <v>96</v>
       </c>
@@ -22235,7 +20672,7 @@
         <v>45412</v>
       </c>
       <c r="G99" s="111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>yyyy04</v>
       </c>
       <c r="H99" s="120" t="s">
@@ -22261,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="O99" s="315">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="P99" s="114">
@@ -22271,31 +20708,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R99" s="322">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>3.68492</v>
       </c>
       <c r="S99" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T99" s="323"/>
-      <c r="U99" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V99" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W99" s="335">
-        <f t="shared" si="15"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X99" s="335">
-        <f t="shared" si="16"/>
-        <v>3.4991495627409139</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="100" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A100" s="111">
         <v>97</v>
       </c>
@@ -22313,7 +20734,7 @@
         <v>45412</v>
       </c>
       <c r="G100" s="111" t="str">
-        <f t="shared" ref="G100:G121" si="17">TEXT(F100,"yyyymm")</f>
+        <f t="shared" ref="G100:G121" si="9">TEXT(F100,"yyyymm")</f>
         <v>yyyy04</v>
       </c>
       <c r="H100" s="120" t="s">
@@ -22338,7 +20759,7 @@
         <v>1</v>
       </c>
       <c r="O100" s="315">
-        <f t="shared" ref="O100:O131" si="18">L100/N100</f>
+        <f t="shared" ref="O100:O131" si="10">L100/N100</f>
         <v>400</v>
       </c>
       <c r="P100" s="114">
@@ -22348,31 +20769,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R100" s="322">
-        <f t="shared" ref="R100:R131" si="19">O100*P100*Q100</f>
+        <f t="shared" ref="R100:R131" si="11">O100*P100*Q100</f>
         <v>368.49200000000002</v>
       </c>
       <c r="S100" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T100" s="323"/>
-      <c r="U100" s="335">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="V100" s="335">
-        <f t="shared" si="14"/>
-        <v>392.59222222222223</v>
-      </c>
-      <c r="W100" s="335">
-        <f t="shared" si="15"/>
-        <v>1.8868885725363865E-2</v>
-      </c>
-      <c r="X100" s="335">
-        <f t="shared" si="16"/>
-        <v>1.4051632468452544</v>
-      </c>
-    </row>
-    <row r="101" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="101" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A101" s="111">
         <v>98</v>
       </c>
@@ -22390,7 +20795,7 @@
         <v>45412</v>
       </c>
       <c r="G101" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H101" s="120" t="s">
@@ -22416,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="O101" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="P101" s="114">
@@ -22426,31 +20831,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R101" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.68492</v>
       </c>
       <c r="S101" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T101" s="323"/>
-      <c r="U101" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V101" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W101" s="335">
-        <f t="shared" si="15"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X101" s="335">
-        <f t="shared" si="16"/>
-        <v>3.4991495627409139</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="102" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A102" s="111">
         <v>99</v>
       </c>
@@ -22468,7 +20857,7 @@
         <v>45412</v>
       </c>
       <c r="G102" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H102" s="120" t="s">
@@ -22493,7 +20882,7 @@
         <v>1</v>
       </c>
       <c r="O102" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>400</v>
       </c>
       <c r="P102" s="114">
@@ -22503,31 +20892,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R102" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>368.49200000000002</v>
       </c>
       <c r="S102" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T102" s="323"/>
-      <c r="U102" s="335">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="V102" s="335">
-        <f t="shared" si="14"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W102" s="335">
-        <f t="shared" si="15"/>
-        <v>7.4636263653231867E-3</v>
-      </c>
-      <c r="X102" s="335">
-        <f t="shared" si="16"/>
-        <v>1.3937579874852137</v>
-      </c>
-    </row>
-    <row r="103" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="103" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A103" s="111">
         <v>100</v>
       </c>
@@ -22545,7 +20918,7 @@
         <v>45412</v>
       </c>
       <c r="G103" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H103" s="120" t="s">
@@ -22571,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="O103" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="P103" s="114">
@@ -22581,31 +20954,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R103" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.68492</v>
       </c>
       <c r="S103" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T103" s="323"/>
-      <c r="U103" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V103" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W103" s="335">
-        <f t="shared" si="15"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X103" s="335">
-        <f t="shared" si="16"/>
-        <v>3.4991495627409139</v>
-      </c>
-    </row>
-    <row r="104" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="104" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A104" s="111">
         <v>101</v>
       </c>
@@ -22623,7 +20980,7 @@
         <v>45412</v>
       </c>
       <c r="G104" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H104" s="120" t="s">
@@ -22648,7 +21005,7 @@
         <v>1</v>
       </c>
       <c r="O104" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>400</v>
       </c>
       <c r="P104" s="114">
@@ -22658,31 +21015,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R104" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>368.49200000000002</v>
       </c>
       <c r="S104" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T104" s="323"/>
-      <c r="U104" s="335">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="V104" s="335">
-        <f t="shared" si="14"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W104" s="335">
-        <f t="shared" si="15"/>
-        <v>7.4636263653231867E-3</v>
-      </c>
-      <c r="X104" s="335">
-        <f t="shared" si="16"/>
-        <v>1.3937579874852137</v>
-      </c>
-    </row>
-    <row r="105" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="105" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A105" s="111">
         <v>102</v>
       </c>
@@ -22700,7 +21041,7 @@
         <v>45412</v>
       </c>
       <c r="G105" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H105" s="120" t="s">
@@ -22726,7 +21067,7 @@
         <v>1</v>
       </c>
       <c r="O105" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="P105" s="114">
@@ -22736,31 +21077,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R105" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.68492</v>
       </c>
       <c r="S105" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T105" s="323"/>
-      <c r="U105" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V105" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W105" s="335">
-        <f t="shared" si="15"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X105" s="335">
-        <f t="shared" si="16"/>
-        <v>3.4991495627409139</v>
-      </c>
-    </row>
-    <row r="106" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="106" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A106" s="111">
         <v>103</v>
       </c>
@@ -22778,7 +21103,7 @@
         <v>45412</v>
       </c>
       <c r="G106" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H106" s="120" t="s">
@@ -22803,7 +21128,7 @@
         <v>1</v>
       </c>
       <c r="O106" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>400</v>
       </c>
       <c r="P106" s="114">
@@ -22813,31 +21138,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R106" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>368.49200000000002</v>
       </c>
       <c r="S106" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T106" s="323"/>
-      <c r="U106" s="335">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="V106" s="335">
-        <f t="shared" si="14"/>
-        <v>397.03666666666663</v>
-      </c>
-      <c r="W106" s="335">
-        <f t="shared" si="15"/>
-        <v>7.4636263653231867E-3</v>
-      </c>
-      <c r="X106" s="335">
-        <f t="shared" si="16"/>
-        <v>1.3937579874852137</v>
-      </c>
-    </row>
-    <row r="107" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="107" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A107" s="111">
         <v>104</v>
       </c>
@@ -22855,7 +21164,7 @@
         <v>45412</v>
       </c>
       <c r="G107" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H107" s="120" t="s">
@@ -22881,7 +21190,7 @@
         <v>1</v>
       </c>
       <c r="O107" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="P107" s="114">
@@ -22891,31 +21200,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R107" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.68492</v>
       </c>
       <c r="S107" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T107" s="323"/>
-      <c r="U107" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V107" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W107" s="335">
-        <f t="shared" si="15"/>
-        <v>0.28027373787271331</v>
-      </c>
-      <c r="X107" s="335">
-        <f t="shared" si="16"/>
-        <v>3.4991495627409139</v>
-      </c>
-    </row>
-    <row r="108" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="108" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A108" s="111">
         <v>105</v>
       </c>
@@ -22933,7 +21226,7 @@
         <v>45412</v>
       </c>
       <c r="G108" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H108" s="120" t="s">
@@ -22958,7 +21251,7 @@
         <v>1</v>
       </c>
       <c r="O108" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
       <c r="P108" s="114">
@@ -22968,31 +21261,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R108" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>184.24600000000001</v>
       </c>
       <c r="S108" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T108" s="323"/>
-      <c r="U108" s="335">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="V108" s="335">
-        <f t="shared" si="14"/>
-        <v>177.77833333333334</v>
-      </c>
-      <c r="W108" s="335">
-        <f t="shared" si="15"/>
-        <v>0.12499648438598628</v>
-      </c>
-      <c r="X108" s="335">
-        <f t="shared" si="16"/>
-        <v>1.2236087730540961</v>
-      </c>
-    </row>
-    <row r="109" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="109" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A109" s="111">
         <v>106</v>
       </c>
@@ -23010,7 +21287,7 @@
         <v>45412</v>
       </c>
       <c r="G109" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H109" s="120" t="s">
@@ -23036,7 +21313,7 @@
         <v>1</v>
       </c>
       <c r="O109" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="P109" s="114">
@@ -23046,31 +21323,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R109" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1.84246</v>
       </c>
       <c r="S109" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T109" s="323"/>
-      <c r="U109" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V109" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W109" s="335">
-        <f t="shared" si="15"/>
-        <v>0.64013686893635668</v>
-      </c>
-      <c r="X109" s="335">
-        <f t="shared" si="16"/>
-        <v>3.8590126938045572</v>
-      </c>
-    </row>
-    <row r="110" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="110" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A110" s="111">
         <v>107</v>
       </c>
@@ -23088,7 +21349,7 @@
         <v>45412</v>
       </c>
       <c r="G110" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H110" s="120" t="s">
@@ -23113,7 +21374,7 @@
         <v>1</v>
       </c>
       <c r="O110" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
       <c r="P110" s="114">
@@ -23123,31 +21384,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R110" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>184.24600000000001</v>
       </c>
       <c r="S110" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T110" s="323"/>
-      <c r="U110" s="335">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="V110" s="335">
-        <f t="shared" si="14"/>
-        <v>177.77833333333334</v>
-      </c>
-      <c r="W110" s="335">
-        <f t="shared" si="15"/>
-        <v>0.12499648438598628</v>
-      </c>
-      <c r="X110" s="335">
-        <f t="shared" si="16"/>
-        <v>1.2236087730540961</v>
-      </c>
-    </row>
-    <row r="111" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="111" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A111" s="111">
         <v>108</v>
       </c>
@@ -23165,7 +21410,7 @@
         <v>45412</v>
       </c>
       <c r="G111" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H111" s="120" t="s">
@@ -23191,7 +21436,7 @@
         <v>1</v>
       </c>
       <c r="O111" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="P111" s="114">
@@ -23201,31 +21446,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R111" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1.84246</v>
       </c>
       <c r="S111" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T111" s="323"/>
-      <c r="U111" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V111" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W111" s="335">
-        <f t="shared" si="15"/>
-        <v>0.64013686893635668</v>
-      </c>
-      <c r="X111" s="335">
-        <f t="shared" si="16"/>
-        <v>3.8590126938045572</v>
-      </c>
-    </row>
-    <row r="112" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="112" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A112" s="111">
         <v>109</v>
       </c>
@@ -23243,7 +21472,7 @@
         <v>45412</v>
       </c>
       <c r="G112" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H112" s="120" t="s">
@@ -23268,7 +21497,7 @@
         <v>1</v>
       </c>
       <c r="O112" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>375</v>
       </c>
       <c r="P112" s="114">
@@ -23278,31 +21507,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R112" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>345.46125000000001</v>
       </c>
       <c r="S112" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T112" s="323"/>
-      <c r="U112" s="335">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="V112" s="335">
-        <f t="shared" si="14"/>
-        <v>341.66666666666669</v>
-      </c>
-      <c r="W112" s="335">
-        <f t="shared" si="15"/>
-        <v>9.7560975609756032E-2</v>
-      </c>
-      <c r="X112" s="335">
-        <f t="shared" si="16"/>
-        <v>1.1961732642778657</v>
-      </c>
-    </row>
-    <row r="113" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="113" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A113" s="111">
         <v>110</v>
       </c>
@@ -23320,7 +21533,7 @@
         <v>45412</v>
       </c>
       <c r="G113" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H113" s="120" t="s">
@@ -23346,7 +21559,7 @@
         <v>1</v>
       </c>
       <c r="O113" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>3.75</v>
       </c>
       <c r="P113" s="114">
@@ -23356,31 +21569,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R113" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.4546125000000001</v>
       </c>
       <c r="S113" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T113" s="323"/>
-      <c r="U113" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V113" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W113" s="335">
-        <f t="shared" si="15"/>
-        <v>0.32525662925566873</v>
-      </c>
-      <c r="X113" s="335">
-        <f t="shared" si="16"/>
-        <v>3.5441324541238695</v>
-      </c>
-    </row>
-    <row r="114" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="114" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A114" s="111">
         <v>111</v>
       </c>
@@ -23398,7 +21595,7 @@
         <v>45412</v>
       </c>
       <c r="G114" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H114" s="120" t="s">
@@ -23423,7 +21620,7 @@
         <v>1</v>
       </c>
       <c r="O114" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>375</v>
       </c>
       <c r="P114" s="114">
@@ -23433,31 +21630,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R114" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>345.46125000000001</v>
       </c>
       <c r="S114" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T114" s="323"/>
-      <c r="U114" s="335">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="V114" s="335">
-        <f t="shared" si="14"/>
-        <v>341.66666666666669</v>
-      </c>
-      <c r="W114" s="335">
-        <f t="shared" si="15"/>
-        <v>9.7560975609756032E-2</v>
-      </c>
-      <c r="X114" s="335">
-        <f t="shared" si="16"/>
-        <v>1.1961732642778657</v>
-      </c>
-    </row>
-    <row r="115" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="115" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A115" s="111">
         <v>112</v>
       </c>
@@ -23475,7 +21656,7 @@
         <v>45412</v>
       </c>
       <c r="G115" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H115" s="120" t="s">
@@ -23501,7 +21682,7 @@
         <v>1</v>
       </c>
       <c r="O115" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>3.75</v>
       </c>
       <c r="P115" s="114">
@@ -23511,31 +21692,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R115" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.4546125000000001</v>
       </c>
       <c r="S115" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T115" s="323"/>
-      <c r="U115" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V115" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W115" s="335">
-        <f t="shared" si="15"/>
-        <v>0.32525662925566873</v>
-      </c>
-      <c r="X115" s="335">
-        <f t="shared" si="16"/>
-        <v>3.5441324541238695</v>
-      </c>
-    </row>
-    <row r="116" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="116" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A116" s="111">
         <v>113</v>
       </c>
@@ -23553,7 +21718,7 @@
         <v>45412</v>
       </c>
       <c r="G116" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H116" s="120" t="s">
@@ -23578,7 +21743,7 @@
         <v>1</v>
       </c>
       <c r="O116" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>216.67</v>
       </c>
       <c r="P116" s="114">
@@ -23588,31 +21753,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R116" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>199.60290409999999</v>
       </c>
       <c r="S116" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T116" s="323"/>
-      <c r="U116" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V116" s="335">
-        <f t="shared" si="14"/>
-        <v>388.89107644305773</v>
-      </c>
-      <c r="W116" s="335">
-        <f t="shared" si="15"/>
-        <v>0.44285170546533414</v>
-      </c>
-      <c r="X116" s="335">
-        <f t="shared" si="16"/>
-        <v>1.1359988860252794</v>
-      </c>
-    </row>
-    <row r="117" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="117" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A117" s="111">
         <v>114</v>
       </c>
@@ -23630,7 +21779,7 @@
         <v>45412</v>
       </c>
       <c r="G117" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H117" s="120" t="s">
@@ -23656,7 +21805,7 @@
         <v>1</v>
       </c>
       <c r="O117" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>2.1667000000000001</v>
       </c>
       <c r="P117" s="114">
@@ -23666,31 +21815,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R117" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1.9960290410000001</v>
       </c>
       <c r="S117" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T117" s="323"/>
-      <c r="U117" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V117" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W117" s="335">
-        <f t="shared" si="15"/>
-        <v>0.61014227696220202</v>
-      </c>
-      <c r="X117" s="335">
-        <f t="shared" si="16"/>
-        <v>3.8290181018304024</v>
-      </c>
-    </row>
-    <row r="118" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="118" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A118" s="111">
         <v>115</v>
       </c>
@@ -23708,7 +21841,7 @@
         <v>45412</v>
       </c>
       <c r="G118" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H118" s="120" t="s">
@@ -23733,7 +21866,7 @@
         <v>1</v>
       </c>
       <c r="O118" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>650</v>
       </c>
       <c r="P118" s="114">
@@ -23743,31 +21876,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R118" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>598.79949999999997</v>
       </c>
       <c r="S118" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T118" s="323"/>
-      <c r="U118" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V118" s="335">
-        <f t="shared" si="14"/>
-        <v>650</v>
-      </c>
-      <c r="W118" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X118" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="119" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="119" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A119" s="111">
         <v>116</v>
       </c>
@@ -23785,7 +21902,7 @@
         <v>45412</v>
       </c>
       <c r="G119" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H119" s="120" t="s">
@@ -23811,7 +21928,7 @@
         <v>1</v>
       </c>
       <c r="O119" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
       <c r="P119" s="114">
@@ -23821,31 +21938,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R119" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>5.9879949999999997</v>
       </c>
       <c r="S119" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T119" s="323"/>
-      <c r="U119" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V119" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W119" s="335">
-        <f t="shared" si="15"/>
-        <v>0.16955517595684083</v>
-      </c>
-      <c r="X119" s="335">
-        <f t="shared" si="16"/>
-        <v>3.3884310008250416</v>
-      </c>
-    </row>
-    <row r="120" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="120" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A120" s="111">
         <v>117</v>
       </c>
@@ -23863,7 +21964,7 @@
         <v>45412</v>
       </c>
       <c r="G120" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H120" s="120" t="s">
@@ -23888,7 +21989,7 @@
         <v>1</v>
       </c>
       <c r="O120" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>650</v>
       </c>
       <c r="P120" s="114">
@@ -23898,31 +21999,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R120" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>149.69987499999999</v>
       </c>
       <c r="S120" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T120" s="323"/>
-      <c r="U120" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V120" s="335">
-        <f t="shared" si="14"/>
-        <v>650</v>
-      </c>
-      <c r="W120" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X120" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="121" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="121" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A121" s="111">
         <v>118</v>
       </c>
@@ -23940,7 +22025,7 @@
         <v>45412</v>
       </c>
       <c r="G121" s="111" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="9"/>
         <v>yyyy04</v>
       </c>
       <c r="H121" s="120" t="s">
@@ -23966,7 +22051,7 @@
         <v>1</v>
       </c>
       <c r="O121" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
       <c r="P121" s="114">
@@ -23976,31 +22061,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R121" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1.4969987499999999</v>
       </c>
       <c r="S121" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T121" s="323"/>
-      <c r="U121" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V121" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W121" s="335">
-        <f t="shared" si="15"/>
-        <v>0.16955517595684083</v>
-      </c>
-      <c r="X121" s="335">
-        <f t="shared" si="16"/>
-        <v>3.3884310008250416</v>
-      </c>
-    </row>
-    <row r="122" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="122" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A122" s="111">
         <v>119</v>
       </c>
@@ -24043,7 +22112,7 @@
         <v>1</v>
       </c>
       <c r="O122" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>1125</v>
       </c>
       <c r="P122" s="114">
@@ -24053,7 +22122,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R122" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1036.38375</v>
       </c>
       <c r="S122" s="322" t="s">
@@ -24062,24 +22131,8 @@
       <c r="T122" s="323">
         <v>45389</v>
       </c>
-      <c r="U122" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V122" s="335">
-        <f t="shared" si="14"/>
-        <v>1125</v>
-      </c>
-      <c r="W122" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X122" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="123" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="123" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A123" s="111">
         <v>120</v>
       </c>
@@ -24123,7 +22176,7 @@
         <v>1</v>
       </c>
       <c r="O123" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>11.25</v>
       </c>
       <c r="P123" s="114">
@@ -24133,7 +22186,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R123" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>10.363837500000001</v>
       </c>
       <c r="S123" s="322" t="s">
@@ -24142,24 +22195,8 @@
       <c r="T123" s="323">
         <v>45389</v>
       </c>
-      <c r="U123" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V123" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W123" s="335">
-        <f t="shared" si="15"/>
-        <v>1.0242301122329938</v>
-      </c>
-      <c r="X123" s="335">
-        <f t="shared" si="16"/>
-        <v>4.2431059371011948</v>
-      </c>
-    </row>
-    <row r="124" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="124" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A124" s="111">
         <v>121</v>
       </c>
@@ -24202,7 +22239,7 @@
         <v>1</v>
       </c>
       <c r="O124" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>1100</v>
       </c>
       <c r="P124" s="114">
@@ -24212,7 +22249,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R124" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>1013.353</v>
       </c>
       <c r="S124" s="322" t="s">
@@ -24221,24 +22258,8 @@
       <c r="T124" s="323">
         <v>45398</v>
       </c>
-      <c r="U124" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V124" s="335">
-        <f t="shared" si="14"/>
-        <v>1100</v>
-      </c>
-      <c r="W124" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X124" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="125" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="125" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A125" s="111">
         <v>122</v>
       </c>
@@ -24282,7 +22303,7 @@
         <v>1</v>
       </c>
       <c r="O125" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="P125" s="114">
@@ -24292,7 +22313,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R125" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>10.13353</v>
       </c>
       <c r="S125" s="322" t="s">
@@ -24301,24 +22322,8 @@
       <c r="T125" s="323">
         <v>45398</v>
       </c>
-      <c r="U125" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V125" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W125" s="335">
-        <f t="shared" si="15"/>
-        <v>0.97924722085003835</v>
-      </c>
-      <c r="X125" s="335">
-        <f t="shared" si="16"/>
-        <v>4.1981230457182388</v>
-      </c>
-    </row>
-    <row r="126" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="126" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A126" s="111">
         <v>123</v>
       </c>
@@ -24361,7 +22366,7 @@
         <v>1</v>
       </c>
       <c r="O126" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>890</v>
       </c>
       <c r="P126" s="114">
@@ -24371,7 +22376,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R126" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>819.89469999999994</v>
       </c>
       <c r="S126" s="322" t="s">
@@ -24380,24 +22385,8 @@
       <c r="T126" s="323">
         <v>45398</v>
       </c>
-      <c r="U126" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V126" s="335">
-        <f t="shared" si="14"/>
-        <v>890</v>
-      </c>
-      <c r="W126" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X126" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="127" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="127" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A127" s="111">
         <v>124</v>
       </c>
@@ -24441,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="O127" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>8.9</v>
       </c>
       <c r="P127" s="114">
@@ -24451,7 +22440,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R127" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>8.1989470000000004</v>
       </c>
       <c r="S127" s="322" t="s">
@@ -24460,24 +22449,8 @@
       <c r="T127" s="323">
         <v>45398</v>
       </c>
-      <c r="U127" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V127" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W127" s="335">
-        <f t="shared" si="15"/>
-        <v>0.60139093323321291</v>
-      </c>
-      <c r="X127" s="335">
-        <f t="shared" si="16"/>
-        <v>3.8202667581014134</v>
-      </c>
-    </row>
-    <row r="128" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="128" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A128" s="111">
         <v>125</v>
       </c>
@@ -24520,7 +22493,7 @@
         <v>1</v>
       </c>
       <c r="O128" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>350</v>
       </c>
       <c r="P128" s="114">
@@ -24530,7 +22503,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R128" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>322.43049999999999</v>
       </c>
       <c r="S128" s="322" t="s">
@@ -24539,24 +22512,8 @@
       <c r="T128" s="323">
         <v>45398</v>
       </c>
-      <c r="U128" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V128" s="335">
-        <f t="shared" si="14"/>
-        <v>350</v>
-      </c>
-      <c r="W128" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X128" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="129" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="129" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A129" s="111">
         <v>126</v>
       </c>
@@ -24600,7 +22557,7 @@
         <v>1</v>
       </c>
       <c r="O129" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
       <c r="P129" s="114">
@@ -24610,7 +22567,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R129" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>3.2243050000000002</v>
       </c>
       <c r="S129" s="322" t="s">
@@ -24619,24 +22576,8 @@
       <c r="T129" s="323">
         <v>45398</v>
       </c>
-      <c r="U129" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V129" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W129" s="335">
-        <f t="shared" si="15"/>
-        <v>0.37023952063862414</v>
-      </c>
-      <c r="X129" s="335">
-        <f t="shared" si="16"/>
-        <v>3.5891153455068245</v>
-      </c>
-    </row>
-    <row r="130" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="130" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A130" s="111">
         <v>127</v>
       </c>
@@ -24679,7 +22620,7 @@
         <v>1</v>
       </c>
       <c r="O130" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>230</v>
       </c>
       <c r="P130" s="114">
@@ -24689,7 +22630,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R130" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>211.88290000000001</v>
       </c>
       <c r="S130" s="322" t="s">
@@ -24698,24 +22639,8 @@
       <c r="T130" s="323">
         <v>45398</v>
       </c>
-      <c r="U130" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V130" s="335">
-        <f t="shared" si="14"/>
-        <v>230</v>
-      </c>
-      <c r="W130" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X130" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="131" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="131" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A131" s="111">
         <v>128</v>
       </c>
@@ -24759,7 +22684,7 @@
         <v>1</v>
       </c>
       <c r="O131" s="315">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>2.3000000000000003</v>
       </c>
       <c r="P131" s="114">
@@ -24769,7 +22694,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R131" s="322">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>2.1188290000000003</v>
       </c>
       <c r="S131" s="322" t="s">
@@ -24778,24 +22703,8 @@
       <c r="T131" s="323">
         <v>45398</v>
       </c>
-      <c r="U131" s="335">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="V131" s="335">
-        <f t="shared" si="14"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W131" s="335">
-        <f t="shared" si="15"/>
-        <v>0.5861573992768101</v>
-      </c>
-      <c r="X131" s="335">
-        <f t="shared" si="16"/>
-        <v>3.8050332241450109</v>
-      </c>
-    </row>
-    <row r="132" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="132" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A132" s="111">
         <v>129</v>
       </c>
@@ -24838,7 +22747,7 @@
         <v>1</v>
       </c>
       <c r="O132" s="315">
-        <f t="shared" ref="O132:O163" si="20">L132/N132</f>
+        <f t="shared" ref="O132:O163" si="12">L132/N132</f>
         <v>690</v>
       </c>
       <c r="P132" s="114">
@@ -24848,7 +22757,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R132" s="322">
-        <f t="shared" ref="R132:R163" si="21">O132*P132*Q132</f>
+        <f t="shared" ref="R132:R163" si="13">O132*P132*Q132</f>
         <v>635.64869999999996</v>
       </c>
       <c r="S132" s="322" t="s">
@@ -24857,24 +22766,8 @@
       <c r="T132" s="323">
         <v>45398</v>
       </c>
-      <c r="U132" s="335">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="V132" s="335">
-        <f t="shared" si="14"/>
-        <v>690</v>
-      </c>
-      <c r="W132" s="335">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X132" s="335">
-        <f t="shared" si="16"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="133" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="133" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A133" s="111">
         <v>130</v>
       </c>
@@ -24918,7 +22811,7 @@
         <v>1</v>
       </c>
       <c r="O133" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>6.9</v>
       </c>
       <c r="P133" s="114">
@@ -24928,7 +22821,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R133" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>6.3564870000000004</v>
       </c>
       <c r="S133" s="322" t="s">
@@ -24937,24 +22830,8 @@
       <c r="T133" s="323">
         <v>45398</v>
       </c>
-      <c r="U133" s="335">
-        <f t="shared" ref="U133:U164" si="22">COUNTIFS($K$4:$K$1000,K133,$F$4:$F$1000,F133)</f>
-        <v>24</v>
-      </c>
-      <c r="V133" s="335">
-        <f t="shared" ref="V133:V164" si="23">AVERAGEIFS($O$4:$O$1000,$K$4:$K$1000,K133)</f>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W133" s="335">
-        <f t="shared" ref="W133:W164" si="24">IFERROR(ABS(O133-V133)/V133,0)</f>
-        <v>0.24152780216956957</v>
-      </c>
-      <c r="X133" s="335">
-        <f t="shared" ref="X133:X164" si="25">LN(1+U133) + W133</f>
-        <v>3.46040362703777</v>
-      </c>
-    </row>
-    <row r="134" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="134" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A134" s="111">
         <v>131</v>
       </c>
@@ -24997,7 +22874,7 @@
         <v>1</v>
       </c>
       <c r="O134" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>60</v>
       </c>
       <c r="P134" s="114">
@@ -25007,7 +22884,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R134" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>55.273800000000001</v>
       </c>
       <c r="S134" s="322" t="s">
@@ -25016,24 +22893,8 @@
       <c r="T134" s="323">
         <v>45400</v>
       </c>
-      <c r="U134" s="335">
-        <f t="shared" si="22"/>
-        <v>2</v>
-      </c>
-      <c r="V134" s="335">
-        <f t="shared" si="23"/>
-        <v>660.82333333333327</v>
-      </c>
-      <c r="W134" s="335">
-        <f t="shared" si="24"/>
-        <v>0.9092041745902838</v>
-      </c>
-      <c r="X134" s="335">
-        <f t="shared" si="25"/>
-        <v>2.0078164632583935</v>
-      </c>
-    </row>
-    <row r="135" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="135" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A135" s="111">
         <v>132</v>
       </c>
@@ -25077,7 +22938,7 @@
         <v>1</v>
       </c>
       <c r="O135" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>0.6</v>
       </c>
       <c r="P135" s="114">
@@ -25087,7 +22948,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R135" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0.55273799999999995</v>
       </c>
       <c r="S135" s="322" t="s">
@@ -25096,24 +22957,8 @@
       <c r="T135" s="323">
         <v>45400</v>
       </c>
-      <c r="U135" s="335">
-        <f t="shared" si="22"/>
-        <v>24</v>
-      </c>
-      <c r="V135" s="335">
-        <f t="shared" si="23"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W135" s="335">
-        <f t="shared" si="24"/>
-        <v>0.89204106068090705</v>
-      </c>
-      <c r="X135" s="335">
-        <f t="shared" si="25"/>
-        <v>4.1109168855491074</v>
-      </c>
-    </row>
-    <row r="136" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="136" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A136" s="111">
         <v>133</v>
       </c>
@@ -25156,7 +23001,7 @@
         <v>1</v>
       </c>
       <c r="O136" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>3450</v>
       </c>
       <c r="P136" s="114">
@@ -25166,7 +23011,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R136" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>3178.2435</v>
       </c>
       <c r="S136" s="322" t="s">
@@ -25175,24 +23020,8 @@
       <c r="T136" s="323">
         <v>45344</v>
       </c>
-      <c r="U136" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V136" s="335">
-        <f t="shared" si="23"/>
-        <v>1810</v>
-      </c>
-      <c r="W136" s="335">
-        <f t="shared" si="24"/>
-        <v>0.90607734806629836</v>
-      </c>
-      <c r="X136" s="335">
-        <f t="shared" si="25"/>
-        <v>1.5992245286262436</v>
-      </c>
-    </row>
-    <row r="137" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="137" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A137" s="111">
         <v>134</v>
       </c>
@@ -25236,7 +23065,7 @@
         <v>1</v>
       </c>
       <c r="O137" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>34.5</v>
       </c>
       <c r="P137" s="114">
@@ -25246,7 +23075,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R137" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>31.782435</v>
       </c>
       <c r="S137" s="322" t="s">
@@ -25255,24 +23084,8 @@
       <c r="T137" s="323">
         <v>45344</v>
       </c>
-      <c r="U137" s="335">
-        <f t="shared" si="22"/>
-        <v>24</v>
-      </c>
-      <c r="V137" s="335">
-        <f t="shared" si="23"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W137" s="335">
-        <f t="shared" si="24"/>
-        <v>5.2076390108478474</v>
-      </c>
-      <c r="X137" s="335">
-        <f t="shared" si="25"/>
-        <v>8.4265148357160484</v>
-      </c>
-    </row>
-    <row r="138" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="138" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A138" s="111">
         <v>135</v>
       </c>
@@ -25315,7 +23128,7 @@
         <v>1</v>
       </c>
       <c r="O138" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>888.64</v>
       </c>
       <c r="P138" s="114">
@@ -25325,7 +23138,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R138" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>818.64182719999997</v>
       </c>
       <c r="S138" s="322" t="s">
@@ -25334,24 +23147,8 @@
       <c r="T138" s="323">
         <v>45407</v>
       </c>
-      <c r="U138" s="335">
-        <f t="shared" si="22"/>
-        <v>2</v>
-      </c>
-      <c r="V138" s="335">
-        <f t="shared" si="23"/>
-        <v>660.82333333333327</v>
-      </c>
-      <c r="W138" s="335">
-        <f t="shared" si="24"/>
-        <v>0.34474670486816961</v>
-      </c>
-      <c r="X138" s="335">
-        <f t="shared" si="25"/>
-        <v>1.4433589935362794</v>
-      </c>
-    </row>
-    <row r="139" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="139" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A139" s="111">
         <v>136</v>
       </c>
@@ -25395,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="O139" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>8.8864000000000001</v>
       </c>
       <c r="P139" s="114">
@@ -25405,7 +23202,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R139" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>8.1864182719999992</v>
       </c>
       <c r="S139" s="322" t="s">
@@ -25414,24 +23211,8 @@
       <c r="T139" s="323">
         <v>45407</v>
       </c>
-      <c r="U139" s="335">
-        <f t="shared" si="22"/>
-        <v>24</v>
-      </c>
-      <c r="V139" s="335">
-        <f t="shared" si="23"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W139" s="335">
-        <f t="shared" si="24"/>
-        <v>0.59894386394198007</v>
-      </c>
-      <c r="X139" s="335">
-        <f t="shared" si="25"/>
-        <v>3.8178196888101805</v>
-      </c>
-    </row>
-    <row r="140" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="140" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A140" s="111">
         <v>137</v>
       </c>
@@ -25474,7 +23255,7 @@
         <v>1</v>
       </c>
       <c r="O140" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>178</v>
       </c>
       <c r="P140" s="114">
@@ -25484,7 +23265,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R140" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>163.97893999999999</v>
       </c>
       <c r="S140" s="322" t="s">
@@ -25493,24 +23274,8 @@
       <c r="T140" s="323">
         <v>45407</v>
       </c>
-      <c r="U140" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V140" s="335">
-        <f t="shared" si="23"/>
-        <v>178</v>
-      </c>
-      <c r="W140" s="335">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X140" s="335">
-        <f t="shared" si="25"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="141" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="141" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A141" s="111">
         <v>138</v>
       </c>
@@ -25528,7 +23293,7 @@
         <v>45412</v>
       </c>
       <c r="G141" s="111" t="str">
-        <f t="shared" ref="G141:G164" si="26">TEXT(F141,"yyyymm")</f>
+        <f t="shared" ref="G141:G164" si="14">TEXT(F141,"yyyymm")</f>
         <v>yyyy04</v>
       </c>
       <c r="H141" s="120" t="s">
@@ -25554,7 +23319,7 @@
         <v>1</v>
       </c>
       <c r="O141" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1.78</v>
       </c>
       <c r="P141" s="114">
@@ -25564,7 +23329,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R141" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>1.6397894</v>
       </c>
       <c r="S141" s="322" t="s">
@@ -25573,24 +23338,8 @@
       <c r="T141" s="323">
         <v>45407</v>
       </c>
-      <c r="U141" s="335">
-        <f t="shared" si="22"/>
-        <v>24</v>
-      </c>
-      <c r="V141" s="335">
-        <f t="shared" si="23"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W141" s="335">
-        <f t="shared" si="24"/>
-        <v>0.67972181335335735</v>
-      </c>
-      <c r="X141" s="335">
-        <f t="shared" si="25"/>
-        <v>3.8985976382215579</v>
-      </c>
-    </row>
-    <row r="142" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="142" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A142" s="111">
         <v>139</v>
       </c>
@@ -25608,7 +23357,7 @@
         <v>45412</v>
       </c>
       <c r="G142" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H142" s="120" t="s">
@@ -25634,7 +23383,7 @@
         <v>32.511099999999999</v>
       </c>
       <c r="O142" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>24000</v>
       </c>
       <c r="P142" s="114">
@@ -25644,7 +23393,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R142" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>22109.52</v>
       </c>
       <c r="S142" s="322" t="s">
@@ -25653,24 +23402,8 @@
       <c r="T142" s="323">
         <v>45409</v>
       </c>
-      <c r="U142" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V142" s="335">
-        <f t="shared" si="23"/>
-        <v>24000</v>
-      </c>
-      <c r="W142" s="335">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X142" s="335">
-        <f t="shared" si="25"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="143" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="143" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A143" s="111">
         <v>140</v>
       </c>
@@ -25688,7 +23421,7 @@
         <v>45412</v>
       </c>
       <c r="G143" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H143" s="120" t="s">
@@ -25714,7 +23447,7 @@
         <v>32.511099999999999</v>
       </c>
       <c r="O143" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>2080</v>
       </c>
       <c r="P143" s="114">
@@ -25724,7 +23457,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R143" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>1916.1584</v>
       </c>
       <c r="S143" s="322" t="s">
@@ -25733,24 +23466,8 @@
       <c r="T143" s="323">
         <v>45409</v>
       </c>
-      <c r="U143" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V143" s="335">
-        <f t="shared" si="23"/>
-        <v>2080</v>
-      </c>
-      <c r="W143" s="335">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X143" s="335">
-        <f t="shared" si="25"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="144" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="144" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A144" s="111">
         <v>141</v>
       </c>
@@ -25768,7 +23485,7 @@
         <v>45412</v>
       </c>
       <c r="G144" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H144" s="120" t="s">
@@ -25794,7 +23511,7 @@
         <v>32.511099999999999</v>
       </c>
       <c r="O144" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>15285</v>
       </c>
       <c r="P144" s="114">
@@ -25804,7 +23521,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R144" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>14081.000550000001</v>
       </c>
       <c r="S144" s="322" t="s">
@@ -25813,24 +23530,8 @@
       <c r="T144" s="323">
         <v>45409</v>
       </c>
-      <c r="U144" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V144" s="335">
-        <f t="shared" si="23"/>
-        <v>15285</v>
-      </c>
-      <c r="W144" s="335">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X144" s="335">
-        <f t="shared" si="25"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="145" spans="1:24" s="93" customFormat="1" ht="20.5" customHeight="1">
+    </row>
+    <row r="145" spans="1:20" s="93" customFormat="1" ht="20.5" customHeight="1">
       <c r="A145" s="111">
         <v>142</v>
       </c>
@@ -25848,7 +23549,7 @@
         <v>45412</v>
       </c>
       <c r="G145" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H145" s="120" t="s">
@@ -25873,7 +23574,7 @@
         <v>32.511099999999999</v>
       </c>
       <c r="O145" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>2715.0001076555391</v>
       </c>
       <c r="P145" s="114">
@@ -25883,7 +23584,7 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R145" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>2501.1395491755125</v>
       </c>
       <c r="S145" s="322" t="s">
@@ -25892,24 +23593,8 @@
       <c r="T145" s="323">
         <v>45409</v>
       </c>
-      <c r="U145" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V145" s="335">
-        <f t="shared" si="23"/>
-        <v>2715.0001076555391</v>
-      </c>
-      <c r="W145" s="335">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X145" s="335">
-        <f t="shared" si="25"/>
-        <v>0.69314718055994529</v>
-      </c>
-    </row>
-    <row r="146" spans="1:24" s="126" customFormat="1" ht="16.25" customHeight="1">
+    </row>
+    <row r="146" spans="1:20" s="126" customFormat="1" ht="16.25" customHeight="1">
       <c r="A146" s="111">
         <v>143</v>
       </c>
@@ -25927,7 +23612,7 @@
         <v>45412</v>
       </c>
       <c r="G146" s="122" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H146" s="124" t="s">
@@ -25952,7 +23637,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O146" s="329">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1999.9999999999998</v>
       </c>
       <c r="P146" s="125">
@@ -25962,31 +23647,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R146" s="331">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>460.61499999999995</v>
       </c>
       <c r="S146" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T146" s="323"/>
-      <c r="U146" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V146" s="335">
-        <f t="shared" si="23"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W146" s="335">
-        <f t="shared" si="24"/>
-        <v>1.330597000190167</v>
-      </c>
-      <c r="X146" s="335">
-        <f t="shared" si="25"/>
-        <v>2.9400349126242675</v>
-      </c>
-    </row>
-    <row r="147" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="147" spans="1:20" ht="16.25" customHeight="1">
       <c r="A147" s="111">
         <v>144</v>
       </c>
@@ -26004,7 +23673,7 @@
         <v>45412</v>
       </c>
       <c r="G147" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H147" s="120" t="s">
@@ -26029,7 +23698,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O147" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1073.8699004305288</v>
       </c>
       <c r="P147" s="114">
@@ -26039,31 +23708,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R147" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>247.32029209340402</v>
       </c>
       <c r="S147" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T147" s="323"/>
-      <c r="U147" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V147" s="335">
-        <f t="shared" si="23"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W147" s="335">
-        <f t="shared" si="24"/>
-        <v>0.25137898426895205</v>
-      </c>
-      <c r="X147" s="335">
-        <f t="shared" si="25"/>
-        <v>1.8608168967030523</v>
-      </c>
-    </row>
-    <row r="148" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="148" spans="1:20" ht="16.25" customHeight="1">
       <c r="A148" s="111">
         <v>145</v>
       </c>
@@ -26081,7 +23734,7 @@
         <v>45412</v>
       </c>
       <c r="G148" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H148" s="120" t="s">
@@ -26106,7 +23759,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O148" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>504.26938540535019</v>
       </c>
       <c r="P148" s="114">
@@ -26116,31 +23769,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R148" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>116.13702147924269</v>
       </c>
       <c r="S148" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T148" s="323"/>
-      <c r="U148" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V148" s="335">
-        <f t="shared" si="23"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W148" s="335">
-        <f t="shared" si="24"/>
-        <v>0.41237564154327572</v>
-      </c>
-      <c r="X148" s="335">
-        <f t="shared" si="25"/>
-        <v>2.0218135539773758</v>
-      </c>
-    </row>
-    <row r="149" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="149" spans="1:20" ht="16.25" customHeight="1">
       <c r="A149" s="111">
         <v>146</v>
       </c>
@@ -26158,7 +23795,7 @@
         <v>45412</v>
       </c>
       <c r="G149" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H149" s="120" t="s">
@@ -26183,7 +23820,7 @@
         <v>1</v>
       </c>
       <c r="O149" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>83.33</v>
       </c>
       <c r="P149" s="114">
@@ -26193,31 +23830,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R149" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>19.191523974999999</v>
       </c>
       <c r="S149" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T149" s="323"/>
-      <c r="U149" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V149" s="335">
-        <f t="shared" si="23"/>
-        <v>858.14922092356937</v>
-      </c>
-      <c r="W149" s="335">
-        <f t="shared" si="24"/>
-        <v>0.90289567598707665</v>
-      </c>
-      <c r="X149" s="335">
-        <f t="shared" si="25"/>
-        <v>2.512333588421177</v>
-      </c>
-    </row>
-    <row r="150" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="150" spans="1:20" ht="16.25" customHeight="1">
       <c r="A150" s="111">
         <v>147</v>
       </c>
@@ -26235,7 +23856,7 @@
         <v>45412</v>
       </c>
       <c r="G150" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H150" s="120" t="s">
@@ -26260,7 +23881,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O150" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
       <c r="P150" s="114">
@@ -26270,31 +23891,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R150" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>806.07624999999996</v>
       </c>
       <c r="S150" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T150" s="323"/>
-      <c r="U150" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V150" s="335">
-        <f t="shared" si="23"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W150" s="335">
-        <f t="shared" si="24"/>
-        <v>1.2305012327485951</v>
-      </c>
-      <c r="X150" s="335">
-        <f t="shared" si="25"/>
-        <v>2.8399391451826954</v>
-      </c>
-    </row>
-    <row r="151" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="151" spans="1:20" ht="16.25" customHeight="1">
       <c r="A151" s="111">
         <v>148</v>
       </c>
@@ -26312,7 +23917,7 @@
         <v>45412</v>
       </c>
       <c r="G151" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H151" s="120" t="s">
@@ -26337,7 +23942,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O151" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1236.4411264937742</v>
       </c>
       <c r="P151" s="114">
@@ -26347,31 +23952,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R151" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>284.76166473996489</v>
       </c>
       <c r="S151" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T151" s="323"/>
-      <c r="U151" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V151" s="335">
-        <f t="shared" si="23"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W151" s="335">
-        <f t="shared" si="24"/>
-        <v>0.21203329803845003</v>
-      </c>
-      <c r="X151" s="335">
-        <f t="shared" si="25"/>
-        <v>1.8214712104725503</v>
-      </c>
-    </row>
-    <row r="152" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="152" spans="1:20" ht="16.25" customHeight="1">
       <c r="A152" s="111">
         <v>149</v>
       </c>
@@ -26389,7 +23978,7 @@
         <v>45412</v>
       </c>
       <c r="G152" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H152" s="120" t="s">
@@ -26414,7 +24003,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O152" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1666.1234760485436</v>
       </c>
       <c r="P152" s="114">
@@ -26424,31 +24013,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R152" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>383.72073246004993</v>
       </c>
       <c r="S152" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T152" s="323"/>
-      <c r="U152" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V152" s="335">
-        <f t="shared" si="23"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W152" s="335">
-        <f t="shared" si="24"/>
-        <v>6.1797276353614511E-2</v>
-      </c>
-      <c r="X152" s="335">
-        <f t="shared" si="25"/>
-        <v>1.6712351887877148</v>
-      </c>
-    </row>
-    <row r="153" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="153" spans="1:20" ht="16.25" customHeight="1">
       <c r="A153" s="111">
         <v>150</v>
       </c>
@@ -26466,7 +24039,7 @@
         <v>45412</v>
       </c>
       <c r="G153" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H153" s="120" t="s">
@@ -26491,7 +24064,7 @@
         <v>1</v>
       </c>
       <c r="O153" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>83.33</v>
       </c>
       <c r="P153" s="114">
@@ -26501,31 +24074,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R153" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>19.191523974999999</v>
       </c>
       <c r="S153" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T153" s="323"/>
-      <c r="U153" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V153" s="335">
-        <f t="shared" si="23"/>
-        <v>1569.1540307677978</v>
-      </c>
-      <c r="W153" s="335">
-        <f t="shared" si="24"/>
-        <v>0.94689495207858854</v>
-      </c>
-      <c r="X153" s="335">
-        <f t="shared" si="25"/>
-        <v>2.5563328645126888</v>
-      </c>
-    </row>
-    <row r="154" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="154" spans="1:20" ht="16.25" customHeight="1">
       <c r="A154" s="111">
         <v>151</v>
       </c>
@@ -26543,7 +24100,7 @@
         <v>45412</v>
       </c>
       <c r="G154" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H154" s="120" t="s">
@@ -26568,7 +24125,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O154" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>2999.9999999999995</v>
       </c>
       <c r="P154" s="114">
@@ -26578,31 +24135,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R154" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>690.9224999999999</v>
       </c>
       <c r="S154" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T154" s="323"/>
-      <c r="U154" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V154" s="335">
-        <f t="shared" si="23"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W154" s="335">
-        <f t="shared" si="24"/>
-        <v>1.1906706694611919</v>
-      </c>
-      <c r="X154" s="335">
-        <f t="shared" si="25"/>
-        <v>2.8001085818952922</v>
-      </c>
-    </row>
-    <row r="155" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="155" spans="1:20" ht="16.25" customHeight="1">
       <c r="A155" s="111">
         <v>152</v>
       </c>
@@ -26620,7 +24161,7 @@
         <v>45412</v>
       </c>
       <c r="G155" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H155" s="120" t="s">
@@ -26645,7 +24186,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O155" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1044.3132120671885</v>
       </c>
       <c r="P155" s="114">
@@ -26655,31 +24196,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R155" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>240.51316508816402</v>
       </c>
       <c r="S155" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T155" s="323"/>
-      <c r="U155" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V155" s="335">
-        <f t="shared" si="23"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W155" s="335">
-        <f t="shared" si="24"/>
-        <v>0.23741789219786805</v>
-      </c>
-      <c r="X155" s="335">
-        <f t="shared" si="25"/>
-        <v>1.8468558046319683</v>
-      </c>
-    </row>
-    <row r="156" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="156" spans="1:20" ht="16.25" customHeight="1">
       <c r="A156" s="111">
         <v>153</v>
       </c>
@@ -26697,7 +24222,7 @@
         <v>45412</v>
       </c>
       <c r="G156" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H156" s="120" t="s">
@@ -26722,7 +24247,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O156" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1540.4706413982433</v>
       </c>
       <c r="P156" s="114">
@@ -26732,31 +24257,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R156" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>354.78194224382594</v>
       </c>
       <c r="S156" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T156" s="323"/>
-      <c r="U156" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V156" s="335">
-        <f t="shared" si="23"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W156" s="335">
-        <f t="shared" si="24"/>
-        <v>0.12488795042573397</v>
-      </c>
-      <c r="X156" s="335">
-        <f t="shared" si="25"/>
-        <v>1.7343258628598344</v>
-      </c>
-    </row>
-    <row r="157" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="157" spans="1:20" ht="16.25" customHeight="1">
       <c r="A157" s="111">
         <v>154</v>
       </c>
@@ -26774,7 +24283,7 @@
         <v>45412</v>
       </c>
       <c r="G157" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H157" s="120" t="s">
@@ -26799,7 +24308,7 @@
         <v>1</v>
       </c>
       <c r="O157" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>83.33</v>
       </c>
       <c r="P157" s="114">
@@ -26809,31 +24318,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R157" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>19.191523974999999</v>
       </c>
       <c r="S157" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T157" s="323"/>
-      <c r="U157" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V157" s="335">
-        <f t="shared" si="23"/>
-        <v>1369.4436328660331</v>
-      </c>
-      <c r="W157" s="335">
-        <f t="shared" si="24"/>
-        <v>0.93915047103793303</v>
-      </c>
-      <c r="X157" s="335">
-        <f t="shared" si="25"/>
-        <v>2.5485883834720333</v>
-      </c>
-    </row>
-    <row r="158" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="158" spans="1:20" ht="16.25" customHeight="1">
       <c r="A158" s="111">
         <v>155</v>
       </c>
@@ -26851,7 +24344,7 @@
         <v>45412</v>
       </c>
       <c r="G158" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H158" s="120" t="s">
@@ -26876,7 +24369,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O158" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1999.9999999999998</v>
       </c>
       <c r="P158" s="114">
@@ -26886,31 +24379,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R158" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>552.73799999999994</v>
       </c>
       <c r="S158" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T158" s="323"/>
-      <c r="U158" s="335">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V158" s="335">
-        <f t="shared" si="23"/>
-        <v>1218.5390520501373</v>
-      </c>
-      <c r="W158" s="335">
-        <f t="shared" si="24"/>
-        <v>0.64130972793616203</v>
-      </c>
-      <c r="X158" s="335">
-        <f t="shared" si="25"/>
-        <v>1.3344569084961073</v>
-      </c>
-    </row>
-    <row r="159" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="159" spans="1:20" ht="16.25" customHeight="1">
       <c r="A159" s="111">
         <v>156</v>
       </c>
@@ -26928,7 +24405,7 @@
         <v>45412</v>
       </c>
       <c r="G159" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H159" s="120" t="s">
@@ -26954,7 +24431,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O159" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="P159" s="114">
@@ -26964,31 +24441,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R159" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>5.52738</v>
       </c>
       <c r="S159" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T159" s="323"/>
-      <c r="U159" s="335">
-        <f t="shared" si="22"/>
-        <v>24</v>
-      </c>
-      <c r="V159" s="335">
-        <f t="shared" si="23"/>
-        <v>5.5576685338356917</v>
-      </c>
-      <c r="W159" s="335">
-        <f t="shared" si="24"/>
-        <v>2.5986313106364332</v>
-      </c>
-      <c r="X159" s="335">
-        <f t="shared" si="25"/>
-        <v>5.8175071355046342</v>
-      </c>
-    </row>
-    <row r="160" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="160" spans="1:20" ht="16.25" customHeight="1">
       <c r="A160" s="111">
         <v>157</v>
       </c>
@@ -27006,7 +24467,7 @@
         <v>45412</v>
       </c>
       <c r="G160" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H160" s="120" t="s">
@@ -27031,7 +24492,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O160" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>2800</v>
       </c>
       <c r="P160" s="114">
@@ -27041,31 +24502,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R160" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>1289.722</v>
       </c>
       <c r="S160" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T160" s="323"/>
-      <c r="U160" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V160" s="335">
-        <f t="shared" si="23"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W160" s="335">
-        <f t="shared" si="24"/>
-        <v>1.2190987462006524</v>
-      </c>
-      <c r="X160" s="335">
-        <f t="shared" si="25"/>
-        <v>2.8285366586347527</v>
-      </c>
-    </row>
-    <row r="161" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="161" spans="1:20" ht="16.25" customHeight="1">
       <c r="A161" s="111">
         <v>158</v>
       </c>
@@ -27083,7 +24528,7 @@
         <v>45412</v>
       </c>
       <c r="G161" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H161" s="120" t="s">
@@ -27108,7 +24553,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O161" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>1584.6507640262344</v>
       </c>
       <c r="P161" s="114">
@@ -27118,31 +24563,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R161" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>729.91391167194388</v>
       </c>
       <c r="S161" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T161" s="323"/>
-      <c r="U161" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V161" s="335">
-        <f t="shared" si="23"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W161" s="335">
-        <f t="shared" si="24"/>
-        <v>0.25589161557732948</v>
-      </c>
-      <c r="X161" s="335">
-        <f t="shared" si="25"/>
-        <v>1.8653295280114297</v>
-      </c>
-    </row>
-    <row r="162" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="162" spans="1:20" ht="16.25" customHeight="1">
       <c r="A162" s="111">
         <v>159</v>
       </c>
@@ -27160,7 +24589,7 @@
         <v>45412</v>
       </c>
       <c r="G162" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H162" s="120" t="s">
@@ -27185,7 +24614,7 @@
         <v>32.309100000000001</v>
       </c>
       <c r="O162" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>862.03948732709978</v>
       </c>
       <c r="P162" s="114">
@@ -27195,31 +24624,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R162" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>397.06831845517206</v>
       </c>
       <c r="S162" s="322" t="s">
         <v>117</v>
       </c>
       <c r="T162" s="323"/>
-      <c r="U162" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V162" s="335">
-        <f t="shared" si="23"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W162" s="335">
-        <f t="shared" si="24"/>
-        <v>0.31680330517749278</v>
-      </c>
-      <c r="X162" s="335">
-        <f t="shared" si="25"/>
-        <v>1.9262412176115931</v>
-      </c>
-    </row>
-    <row r="163" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="163" spans="1:20" ht="16.25" customHeight="1">
       <c r="A163" s="111">
         <v>160</v>
       </c>
@@ -27237,7 +24650,7 @@
         <v>45412</v>
       </c>
       <c r="G163" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H163" s="120" t="s">
@@ -27262,7 +24675,7 @@
         <v>1</v>
       </c>
       <c r="O163" s="315">
-        <f t="shared" si="20"/>
+        <f t="shared" si="12"/>
         <v>83.33</v>
       </c>
       <c r="P163" s="114">
@@ -27272,31 +24685,15 @@
         <v>0.92122999999999999</v>
       </c>
       <c r="R163" s="322">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>38.383047949999998</v>
       </c>
       <c r="S163" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T163" s="323"/>
-      <c r="U163" s="335">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="V163" s="335">
-        <f t="shared" si="23"/>
-        <v>1261.773503677525</v>
-      </c>
-      <c r="W163" s="335">
-        <f t="shared" si="24"/>
-        <v>0.93395803624253559</v>
-      </c>
-      <c r="X163" s="335">
-        <f t="shared" si="25"/>
-        <v>2.5433959486766358</v>
-      </c>
-    </row>
-    <row r="164" spans="1:24" ht="16.25" customHeight="1" thickBot="1">
+    </row>
+    <row r="164" spans="1:20" ht="16.25" customHeight="1" thickBot="1">
       <c r="A164" s="111">
         <v>161</v>
       </c>
@@ -27310,7 +24707,7 @@
         <v>45412</v>
       </c>
       <c r="G164" s="111" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="14"/>
         <v>yyyy04</v>
       </c>
       <c r="H164" s="120" t="s">
@@ -27327,7 +24724,7 @@
         <v>1</v>
       </c>
       <c r="O164" s="315">
-        <f t="shared" ref="O164" si="27">L164/N164</f>
+        <f t="shared" ref="O164" si="15">L164/N164</f>
         <v>0</v>
       </c>
       <c r="P164" s="114">
@@ -27337,31 +24734,15 @@
         <v>1</v>
       </c>
       <c r="R164" s="322">
-        <f t="shared" ref="R164" si="28">O164*P164*Q164</f>
+        <f t="shared" ref="R164" si="16">O164*P164*Q164</f>
         <v>0</v>
       </c>
       <c r="S164" s="322" t="s">
         <v>188</v>
       </c>
       <c r="T164" s="323"/>
-      <c r="U164" s="335">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="V164" s="335" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W164" s="335">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="X164" s="335">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:24" ht="16.25" customHeight="1">
+    </row>
+    <row r="165" spans="1:20" ht="16.25" customHeight="1">
       <c r="A165" s="95"/>
       <c r="B165" s="95"/>
       <c r="C165" s="96"/>
@@ -27382,10 +24763,6 @@
       <c r="R165" s="100"/>
       <c r="S165" s="100"/>
       <c r="T165" s="317"/>
-      <c r="U165" s="333"/>
-      <c r="V165" s="333"/>
-      <c r="W165" s="333"/>
-      <c r="X165" s="333"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:S164" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
@@ -27395,12 +24772,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27542,15 +24916,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFC8DCB-C5E7-4929-A918-6C29CFB59131}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1697689-65B4-4CBD-BEED-83CCCD4DFFC8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27574,10 +24952,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1697689-65B4-4CBD-BEED-83CCCD4DFFC8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEFC8DCB-C5E7-4929-A918-6C29CFB59131}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>